--- a/upcoming_exhibitions.xlsx
+++ b/upcoming_exhibitions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W313"/>
+  <dimension ref="A1:X313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +544,11 @@
           <t>need</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>lead_gender</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -643,6 +648,11 @@
       <c r="W2" t="inlineStr">
         <is>
           <t>"Apart from You" (1933) by Mikio Naruse meets viewers' desires for emotional depth and social realism by exploring the lives of geishas and their children in 1930s Japan. The film satisfies needs for authentic human drama, addressing themes of maternal sacrifice, class struggle, and the tension between traditional roles and modern aspirations. It appeals to audiences seeking understated, poignant storytelling that examines women's limited options in a patriarchal society, while offering compassionate character studies rather than melodrama.</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -724,6 +734,11 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>I don't have any information about "Battle Club Pro Presents Women Crush Wednesday" in my knowledge base, so I cannot accurately describe what viewer desires or needs this film meets. To provide you with an accurate answer, I would need access to details about the film's content, genre, and target audience.</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -847,6 +862,11 @@
 The film appeals to viewers seeking both meaningful social discourse and compelling dramatic entertainment.</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -950,6 +970,11 @@
       <c r="W5" t="inlineStr">
         <is>
           <t>"Flower Shop Mystery: Snipped in the Bud" meets viewer desires for light, cozy mystery entertainment with a charming small-town setting, amateur detective solving crimes, romantic elements, and visually appealing floral arrangements. It provides comfortable, low-stakes escapism with a likable protagonist, predictable but satisfying plot resolution, and a wholesome atmosphere that appeals to fans of Hallmark-style mysteries who want feel-good content without graphic violence or dark themes.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1050,6 +1075,11 @@
 - **Artistic inspiration** through diverse poetic voices and styles
 - **Educational value** for students of literature and counterculture history
 The documentary appeals to poetry enthusiasts, literary scholars, and those seeking connection to authentic artistic rebellion and creative freedom.</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1174,6 +1204,11 @@
 The film appeals to viewers who appreciate intelligent, morally challenging thrillers that prioritize atmosphere and realism over easy answers.</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1287,6 +1322,11 @@
           <t># Twin Peaks: Viewer Desires Met
 **Twin Peaks: Fire Walk with Me** (1992) satisfies several key viewer desires:
 **Mystery and Puzzle-Solving**: The film's cryptic narrative and symbolism engage viewers who enjoy interpreting hidden meanings and piecing together fragmented storytelling. **Atmospheric Immersion**: Lynch's surreal, dreamlike visuals and haunting sound design appeal to audiences seeking distinctive aesthetic experiences that transcend conventional filmmaking. **Emotional Intensity**: The dark exploration of trauma, abuse, and Laura Palmer's tragic fate provides cathartic engagement with deeply disturbing psychological content. **Cult/Fan Service**: For Twin Peaks enthusiasts, the film offers deeper mythology, answers to series questions, and expanded universe content that rewards dedicated viewership. **Transgressive Art**: The film meets desires for boundary-pushing cinema that challenges mainstream sensibilities and embraces the uncomfortable and taboo. **Auteur Experience**: Viewers seeking Lynch's singular artistic vision find his uncompromised creative style fully realized without network television constraints.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1411,6 +1451,11 @@
 The film satisfies the demand for quality animated sequels that balance entertainment with meaningful storytelling.</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1514,6 +1559,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "Calle Málaga" in my knowledge base. Without details about this particular film's content, themes, or production, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film, I'd be happy to help analyze its appeal to audiences.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1636,6 +1686,11 @@
 The film ultimately serves viewers seeking a serious, critical examination of fraternity culture rather than entertainment or escapism.</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1749,6 +1804,11 @@
           <t>I don't have specific information about a film titled "Good Luck, Have Fun, Don't Die" in my knowledge base. Without being able to verify details about this particular film, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as its release year, director, or subject matter), I would be better able to help you.</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1862,6 +1922,11 @@
           <t>"Blonde Ambition" (1981) meets viewer desires for lighthearted escapist entertainment through its romantic comedy formula, featuring an attractive cast, wish-fulfillment storyline about success and romance, and easily digestible plot that requires minimal emotional investment while providing predictable satisfaction.</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1974,6 +2039,11 @@
         <is>
           <t># Viewer Desires Met by *Once Upon a Time... in Hollywood*
 **Nostalgia and escapism**: The film immerses viewers in a meticulously recreated 1969 Los Angeles, satisfying desires for a bygone Hollywood era. **Wish fulfillment**: Tarantino rewrites history around the Manson murders, offering cathartic justice and a "what if" fantasy that corrects a tragic past. **Star power and chemistry**: The pairing of Leonardo DiCaprio and Brad Pitt delivers charismatic performances and compelling friendship dynamics. **Genre homage**: The film celebrates Western and action B-movies, appealing to cinephiles who appreciate Hollywood history and meta-commentary. **Tension and release**: Slow-burn storytelling builds to Tarantino's signature violent catharsis, satisfying expectations for his distinctive style. **Comfort in uncertainty**: The film addresses anxiety about obsolescence and change while ultimately affirming resilience and second chances.</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -2079,6 +2149,11 @@
 **Escapist corporate thriller entertainment** - offering a glossy, fast-paced story of espionage and betrayal in the tech industry that allows audiences to experience high-stakes intrigue vicariously. **Wish fulfillment** - the protagonist's rapid rise from working-class obscurity to wealth and power satisfies fantasies of sudden success and revenge against corporate elites. **Moral validation** - the narrative confirms suspicions about corporate corruption and the ruthlessness of the wealthy, meeting desires to see systemic injustice exposed. **Accessible complexity** - it provides just enough intellectual stimulation through its corporate espionage plot without demanding too much analytical effort, perfect for casual viewing. **Attractive star power** - the cast of recognizable actors (Liam Hemsworth, Harrison Ford, Gary Oldman) fulfills the desire to watch charismatic performers in a contemporary setting.</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2193,6 +2268,11 @@
 **The Sweet Body of Deborah** (1968) appeals to viewers seeking Italian giallo thrills, combining erotic voyeurism with murder mystery. It satisfies desires for stylish 1960s cinematography, glamorous European locations (Geneva, Nice), sexual titillation through its attractive leads, and suspenseful plot twists involving deception and revenge. The film caters to exploitation cinema fans wanting blend of softcore eroticism, psychological tension, and violent shock moments characteristic of the proto-giallo genre.</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2306,6 +2386,11 @@
           <t>I don't have specific information about a film titled "Good Luck, Have Fun, Don't Die" in my knowledge base. Without being able to verify details about this particular film, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as its release year, director, or subject matter), I'd be happy to help analyze its appeal to audiences.</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2420,6 +2505,11 @@
 *Little Shop of Horrors* satisfies viewers' desires for escapist entertainment through its darkly comedic musical format, blending humor with horror in an accessible way. It fulfills needs for catharsis by exploring themes of ambition, moral compromise, and consequences through exaggerated, fantastical scenarios. The film offers nostalgic pleasure through its 1960s setting and doo-wop musical style, while the underdog protagonist appeals to audiences' desire to root for relatable characters. The campy, over-the-top performances and practical effects provide spectacle and visual novelty, and the romantic subplot satisfies emotional engagement. Ultimately, it delivers wish-fulfillment fantasy (fame and success) while simultaneously cautioning against Faustian bargains, allowing viewers to safely explore darker impulses through satire.</t>
         </is>
       </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2534,6 +2624,11 @@
 *Sinners* (2025), directed by Ryan Coogler, meets viewer desires for visceral horror entertainment, social commentary on racial injustice and identity, and stylish genre filmmaking. The film appeals to fans seeking both supernatural scares and deeper thematic exploration of African American history, particularly around themes of duality, sin, and systemic oppression in the Jim Crow South. Its combination of strong performances, atmospheric tension, and allegorical storytelling satisfies audiences looking for elevated horror that blends entertainment with meaningful cultural critique.</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2644,6 +2739,11 @@
 *The More the Merrier* (1943) meets viewer desires for lighthearted escapism during wartime, romantic wish-fulfillment, and comic relief. The film addresses the real wartime issue of housing shortages in Washington D.C. while providing optimistic humor about Americans pulling together. It satisfies the need for feel-good entertainment that acknowledges contemporary challenges without dwelling on war's darkness, offering charming romance, witty banter, and the reassurance that love and community spirit can flourish even in difficult times.</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2755,6 +2855,11 @@
 - **Moral complexity without easy answers** - The film explores a man's dual life with empathy rather than judgment, satisfying audiences interested in nuanced character studies over simplistic condemnation. - **Human frailty and understanding** - It meets the need to see flawed characters treated with compassion, exploring loneliness, emotional need, and the consequences of deception. - **Women's perspectives in 1950s cinema** - Directed by Ida Lupino, the film unusually centers the emotional experiences of both women involved, appealing to viewers wanting more substantive female characters. - **Social commentary on marriage and domesticity** - It questions 1950s ideals about marriage, family, and male responsibility, satisfying those interested in films that challenge social norms of their era. - **Melodrama with restraint** - The film delivers emotional intensity without sensationalism, appealing to viewers who appreciate measured, thoughtful drama over exploitation.</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2856,6 +2961,7 @@
           <t>I don't have specific information about a film titled "A Life Illuminated" in my knowledge base. This could be a documentary, independent film, or lesser-known work that isn't widely documented. Without details about its content, themes, or subject matter, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as its subject, director, or year of release), I could offer a more helpful response.</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2961,6 +3067,11 @@
           <t>I don't have specific information about a film called "Dead Lover" to provide an accurate summary of what viewer desires or needs it meets. This could refer to multiple films with similar titles, or it may be an obscure or regional production. Without confirmed details about the specific film's plot, themes, and genre, I cannot reliably describe what audience needs it fulfills.</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3068,6 +3179,11 @@
       <c r="W24" t="inlineStr">
         <is>
           <t>"Ghost Elephants" typically appeals to viewers seeking nature documentary content that combines wildlife conservation awareness with stunning cinematography. It meets desires for educational content about endangered species, particularly elephants and their ecosystems, while satisfying interests in environmental issues, African wildlife, and conservation efforts.</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3187,6 +3303,11 @@
 The film essentially serves audiences who value meditative, poetic cinema over conventional narrative entertainment.</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3298,6 +3419,11 @@
       <c r="W26" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "The Ugly Stepsister" in my knowledge base. Without being able to verify details about this specific film, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as release year, director, or plot details), I might be able to help better.</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3419,6 +3545,11 @@
 The film is highly controversial due to its explicit content involving a minor character and was banned in several countries.</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3518,6 +3649,11 @@
 **Spiritual contemplation** - The film offers a meditative space for reflecting on existence, faith, and meaning beyond materialism. **Aesthetic transcendence** - Tarkovsky's painterly compositions and slow cinema provide immersive beauty that elevates viewers beyond everyday experience. **Emotional catharsis** - The exploration of displacement, longing, and alienation resonates with feelings of homesickness and existential melancholy. **Intellectual engagement** - Complex symbolism and philosophical themes challenge viewers seeking substantive, thought-provoking cinema. **Cultural exploration** - The film bridges Russian and Italian identities, appealing to interest in cross-cultural dialogue and artistic heritage. **Escapism through art** - The deliberate pacing and dreamlike atmosphere offer refuge from the speed and superficiality of modern life, meeting desires for contemplative retreat.</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3633,6 +3769,11 @@
 **Visceral thrills and shock value** - The extreme premise of teenagers forced to kill each other delivers intense, transgressive entertainment that pushes boundaries. **Social commentary consumption** - Viewers seeking critique of authority, media violence, and societal pressure find pointed satire about competitive culture and institutional control. **Survival drama tension** - The life-or-death stakes and strategic maneuvering appeal to fans of suspenseful "what would I do?" scenarios. **Cathartic rebellion fantasy** - The film channels youth frustration and anti-establishment sentiment, offering catharsis for feelings about oppressive systems. **Moral complexity exploration** - Audiences interested in ethical dilemmas engage with questions about humanity under extreme duress and the breakdown of civilization. **Genre innovation appreciation** - Film enthusiasts value its influential role in popularizing the "death game" subgenre later seen in *The Hunger Games* and similar works.</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3736,6 +3877,11 @@
       <c r="W30" t="inlineStr">
         <is>
           <t>"By the Bluest of Seas" (1936) meets viewers' desires for escapism, visual beauty, and romantic fantasy through its stunning Caspian Sea cinematography and lighthearted love triangle plot. The film offers relief from Soviet industrial realities with its idyllic seaside setting, poetic imagery, and playful romantic competition between two friends for a local woman's affection. It satisfies needs for entertainment, aesthetic pleasure, and optimistic storytelling while subtly incorporating socialist themes of collective labor and community harmony.</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3856,6 +4002,11 @@
 The film satisfies desires for serious, psychologically challenging art cinema rather than mainstream entertainment.</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3969,6 +4120,11 @@
           <t>The film "Carlos" (2010) meets viewers' desires for an epic, immersive biographical experience of one of history's most notorious terrorists. It satisfies interest in Cold War politics, international intrigue, and the psychology of radicalism through its detailed portrayal of Ilich Ramírez Sánchez (Carlos the Jackal). The film appeals to those seeking a complex character study that avoids simplistic judgments, lengthy substantive storytelling (particularly in its 5.5-hour version), and a globetrotting narrative spanning multiple countries and decades. It also fulfills appreciation for stylish direction and strong lead performance.</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4079,6 +4235,11 @@
 **Certified Copy** meets viewers' desires for intellectual stimulation and philosophical contemplation about authenticity, identity, and relationships. The film appeals to audiences who appreciate ambiguous narratives that resist easy interpretation, offering the pleasure of piecing together whether the protagonists are strangers or an estranged married couple. It satisfies cinephiles interested in art-house cinema, meta-textual exploration of originality versus reproduction, and nuanced performances. The Tuscan setting provides aesthetic pleasure, while the evolving dynamic between the characters fulfills a need for complex, adult relationship drama that mirrors real tensions between appearance and reality in both art and love.</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4190,6 +4351,11 @@
       <c r="W34" t="inlineStr">
         <is>
           <t>"Code Unknown" meets viewers' desires for intellectually challenging cinema that explores contemporary social issues like alienation, communication breakdown, and discrimination in modern urban society. The film appeals to those seeking non-linear, fragmented storytelling that mirrors the disconnection of modern life, and satisfies audiences interested in observational realism and moral ambiguity rather than conventional narrative resolution. It attracts cinephiles who appreciate Haneke's austere directorial style and are willing to engage with uncomfortable themes about privilege, immigration, and the failure of human connection.</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4310,6 +4476,11 @@
 The film appeals to anime fans seeking sophisticated, adult-oriented entertainment with substance beyond typical action fare.</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4431,6 +4602,11 @@
 The film primarily serves viewers interested in confrontational arthouse cinema rather than mainstream entertainment.</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4536,6 +4712,11 @@
           <t># Summary
 *Diary of a Country Priest* meets viewers' desires for:
 **Spiritual contemplation** - The film offers profound meditation on faith, doubt, and religious meaning, appealing to those seeking deeper existential questions. **Artistic cinema** - Its austere visual style, minimalist approach, and literary adaptation satisfy audiences interested in cinema as high art rather than entertainment. **Emotional authenticity** - The raw portrayal of suffering, isolation, and human struggle provides cathartic identification for viewers experiencing their own difficulties. **Intellectual engagement** - The complex theological themes and philosophical questions reward thoughtful, patient viewers seeking mentally stimulating content. **Transcendent experience** - The film's spiritual journey toward grace and redemption offers viewers a sense of meaning beyond everyday material concerns.</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4659,6 +4840,11 @@
 7. **Bittersweet emotion** - Blending humor with poignant moments about friendship, loyalty, and unrealized dreams</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4764,6 +4950,11 @@
 - **Meditative violence** - Action grounded in ritual and meaning rather than spectacle alone</t>
         </is>
       </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4864,6 +5055,11 @@
         <is>
           <t># Viewer Desires Met by "Hero" (2002)
 **Visual Spectacle**: Stunning cinematography with vibrant color palettes and breathtaking martial arts choreography satisfies the desire for aesthetic beauty and visual artistry. **Escapism**: The mythic, stylized ancient China setting offers transportation to a legendary world far removed from everyday life. **Emotional Drama**: Complex relationships and themes of sacrifice, love, and betrayal fulfill the need for emotional depth and human connection. **Philosophical Reflection**: The film's exploration of concepts like sacrifice for the greater good, perspective, and truth appeals to viewers seeking meaningful ideas. **Action and Excitement**: Elaborate, gravity-defying fight sequences provide adrenaline and entertainment for action enthusiasts. **Cultural Experience**: Western audiences especially gain exposure to Chinese history, philosophy, and cinematic traditions, satisfying curiosity about other cultures.</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4987,6 +5183,11 @@
 The film appeals to audiences seeking thought-provoking, uncomfortable, and aesthetically bold cinema rather than conventional entertainment.</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5093,6 +5294,11 @@
 *I Want to Talk About Duras* meets viewers' desires for intimate intellectual engagement and artistic contemplation. The film appeals to those seeking authentic conversations about literature, creativity, and the complexities of artistic interpretation. It satisfies needs for slow-paced, meditative cinema that prioritizes ideas over plot, offering a space for reflection on Marguerite Duras's work and legacy. The documentary-style format fulfills viewers' interest in behind-the-scenes glimpses of filmmaking and literary discourse, while providing a sense of proximity to artistic genius and the creative process.</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5202,6 +5408,11 @@
           <t># Summary: Viewer Desires/Needs Met by "In a Lonely Place"
 **In a Lonely Place** (1950) satisfies several key viewer desires:
 1. **Psychological complexity** - The film offers a nuanced character study of a volatile, potentially dangerous man, appealing to audiences who enjoy morally ambiguous protagonists. 2. **Romance and emotional intensity** - The passionate but doomed love affair between Dixon Steele and Laurel Gray provides romantic escapism tinged with darkness. 3. **Suspense and mystery** - The murder investigation creates tension and keeps viewers questioning the protagonist's innocence. 4. **Exploration of violence and masculinity** - The film examines toxic behavior and rage, allowing viewers to safely confront disturbing aspects of human nature. 5. **Cynicism about Hollywood** - It offers an insider's critique of the film industry, appealing to those interested in Hollywood's darker side. 6. **Existential themes** - The film explores isolation, alienation, and the impossibility of truly knowing another person, resonating with viewers seeking deeper meaning. 7. **Film noir aesthetics** - Atmospheric cinematography</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5323,6 +5534,11 @@
 - **Artistic sophistication** - appeals to cinephiles seeking elevated, auteur-driven cinema
 - **Cultural insight** - glimpse into traditional Asian values around propriety, honor, and social expectations
 - **Melancholic reflection** - meets the need for contemplative, bittersweet emotional experiences</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5450,6 +5666,11 @@
 The film serves viewers who value experiential, mood-driven cinema over straightforward narrative resolution.</t>
         </is>
       </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5568,6 +5789,11 @@
 The film primarily serves niche audiences who value avant-garde art cinema over mainstream entertainment.</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5681,6 +5907,7 @@
 The film satisfies audiences drawn to directors like Tarkovsky or Apichatpong Weerasethakul who value cinema as art and meditation rather than entertainment.</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5794,6 +6021,11 @@
           <t># Kill Bill: Vol. 1 - Viewer Desires and Needs Met
 **Kill Bill: Vol. 1** satisfies several key viewer desires:
 **Visceral Action and Spectacle**: Delivers stylized, choreographed violence and martial arts sequences that provide adrenaline and visual excitement. **Revenge Fantasy**: Fulfills the primal desire for justice and catharsis through the Bride's quest for vengeance against those who wronged her. **Aesthetic Pleasure**: Offers rich cinematic homages to kung fu films, anime, and exploitation cinema with bold visual style and music. **Female Empowerment**: Presents a powerful, skilled female protagonist who takes control of her destiny through strength and determination. **Escapism**: Provides an immersive, heightened reality separate from everyday life through Tarantino's distinctive filmmaking approach. **Narrative Puzzle**: Engages viewers intellectually through non-linear storytelling that encourages active viewing and anticipation for resolution.</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5914,6 +6146,11 @@
 The film essentially meets desires for stylish, intelligent entertainment that challenges conventional morality while delivering visceral noir thrills.</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6031,6 +6268,11 @@
 - **Intellectual engagement** - The film operates on multiple levels, rewarding viewers seeking substance beyond plot mechanics</t>
         </is>
       </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6128,6 +6370,11 @@
           <t>"Krabi, 2562" meets viewer desires for contemplative, unconventional cinema that challenges traditional narrative structures. The film appeals to audiences seeking intellectual engagement with meta-cinematic techniques, as it blurs documentary and fiction while exploring themes of Thai history, mythology, and contemporary social issues. It satisfies those interested in slow cinema, reflexive filmmaking, and critical examination of how stories are constructed and power dynamics are represented in film. The work also appeals to viewers wanting authentic portrayals of working-class Thai life and those who appreciate experimental approaches to discussing colonialism, tourism, and national identity without didactic storytelling.</t>
         </is>
       </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6233,6 +6480,11 @@
           <t>"Le Bon Plaisir" (1984) meets viewer desires for political intrigue, romantic drama, and power dynamics by telling the story of a French president who must confront his secret past when an old lover reveals he fathered her son. The film satisfies audiences interested in behind-the-scenes political maneuvering, forbidden romance, questions of personal responsibility versus public duty, and the tension between private lives and public personas of powerful figures.</t>
         </is>
       </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6348,6 +6600,11 @@
 - **Authentic relationship complexity**: The film portrays messy, ambiguous romantic entanglements without easy resolutions, appealing to those seeking realistic depictions of modern love and dating frustrations. - **Character study intimacy**: Viewers interested in psychological depth get an intimate portrait of a woman navigating desire, self-doubt, and the search for connection in midlife. - **Artistic cinema appreciation**: The film satisfies cinephiles seeking Denis's distinctive directorial style, Binoche's nuanced performance, and contemplative pacing over conventional narrative. - **Emotional recognition**: It validates the experience of romantic confusion and loneliness, offering catharsis for viewers who've felt similarly adrift in relationships.</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6445,6 +6702,11 @@
           <t>I don't have any information about a film called "Liberty at Night" in my knowledge base. This could be a lesser-known, independent, or regional film, or possibly a film released after my training data. Without access to details about this specific film, I cannot accurately describe what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6558,6 +6820,11 @@
           <t>"Lola Montès" satisfies viewers seeking visually sumptuous spectacle through Max Ophüls' elaborate cinematography and innovative use of CinemaScope and color. It appeals to those interested in meta-cinema and narrative experimentation through its circus-framing device and non-linear storytelling. The film meets desires for psychological complexity in its portrayal of a famous courtesan's public humiliation versus private identity, offering both critical commentary on celebrity exploitation and the visual pleasure of lavish period recreations. It also appeals to cinephiles valuing auteur artistry and formally bold, visually-driven cinema over conventional narrative.</t>
         </is>
       </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6671,6 +6938,11 @@
           <t>"Maps to the Stars" appeals to viewers interested in dark satire and critical examinations of Hollywood culture, celebrity worship, and fame's corrupting influence. It satisfies desires for provocative, uncomfortable cinema that exposes the narcissism, dysfunction, and moral decay beneath the entertainment industry's glamorous surface. The film meets needs for psychologically complex storytelling, transgressive content, and unflinching critique of American excess and family pathology.</t>
         </is>
       </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6784,6 +7056,11 @@
           <t># Summary: Viewer Desires/Needs Met by Mauvais Sang
 **Mauvais Sang** (1986) fulfills several audience desires:
 1. **Aesthetic/Visual Pleasure**: Leos Carax's striking cinematography, bold colors, and stylized compositions satisfy viewers seeking artistic, visually innovative cinema. 2. **Emotional Intensity**: The film's passionate exploration of doomed love and existential longing appeals to those craving raw, romantic emotion. 3. **Intellectual Engagement**: Its French New Wave influences, philosophical themes, and non-linear storytelling attract cinephiles who enjoy interpretive, art-house cinema. 4. **Nostalgia for Cinema History**: References to classic films and noir conventions satisfy viewers who appreciate intertextuality and film tradition. 5. **Youth and Rebellion**: The youthful energy, unconventional narrative, and romantic defiance resonate with audiences seeking anti-establishment, bohemian expression. 6. **Escapism through Style**: The film's dreamlike atmosphere and heightened reality offer escape from conventional narrative cinema.</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6875,6 +7152,11 @@
           <t>"Members Only" appeals to viewers seeking insider perspectives on exclusive social spaces and class dynamics. The film satisfies curiosity about private club culture, offers social commentary on privilege and belonging, and explores themes of identity, exclusion, and what it means to be part of an elite group. It meets desires for both voyeuristic glimpses into restricted worlds and critical examination of social hierarchies.</t>
         </is>
       </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6982,6 +7264,11 @@
 1. **Escapist Entertainment** - The film offered thrilling action, mystery, and adventure during a politically tumultuous period in Soviet history. 2. **Modern Spectacle** - It featured exciting chase sequences, exotic locations, and Western-style production values that appealed to audiences hungry for sophisticated cinema. 3. **Ideological Validation** - The anti-capitalist narrative aligned with Soviet propaganda while still delivering entertainment, satisfying both state requirements and audience pleasure. 4. **Genre Thrills** - It combined elements of detective stories, serials, and action films popular in Western cinema, meeting demand for these genres in Soviet contexts. 5. **Romantic Fantasy** - The film included romantic subplots and an appealing female protagonist that provided emotional engagement. 6. **Technological Wonder** - Its depiction of mad scientists, inventions, and conspiracies fed audience fascination with science and modernity.</t>
         </is>
       </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7087,6 +7374,11 @@
           <t>"Mundane History" meets viewers' desires for contemplative, slow cinema that explores themes of caregiving, intimacy, and personal transformation. The film appeals to audiences seeking artistic, meditative narratives that prioritize atmosphere and subtle emotional shifts over conventional plot, offering a quiet examination of the relationship between a paralyzed young man and his caregiver. It satisfies those interested in Thai art-house cinema and philosophical reflections on mortality, dependency, and human connection.</t>
         </is>
       </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7199,6 +7491,11 @@
         <is>
           <t># Viewer Desires Met by *Once Upon a Time... in Hollywood*
 The film satisfies viewers' desire for **nostalgia** through its meticulous recreation of 1969 Los Angeles and Golden Age Hollywood. It meets the need for **escapism** by offering a romanticized, alternate version of history where tragedy is averted. The movie appeals to cinephiles' love of **film history and industry insider knowledge**, showcasing moviemaking processes and era-specific details. It provides **wish fulfillment** by rewriting the Manson murders with a cathartic, heroic ending. The film also delivers Tarantino's signature **stylistic pleasures**—witty dialogue, compelling performances (particularly from DiCaprio and Pitt), and carefully crafted tension—while exploring themes of **aging, relevance, and friendship** that resonate emotionally with audiences.</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7304,6 +7601,7 @@
 The film satisfies audiences interested in contemplative European cinema that prioritizes mood, character psychology, and the bittersweet nature of modern romance over conventional plot-driven narratives.</t>
         </is>
       </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7412,6 +7710,11 @@
 - **Justice and resolution** - Villains are punished and virtue rewarded, satisfying the desire for moral order</t>
         </is>
       </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7509,6 +7812,7 @@
           <t>Frederick Wiseman's documentary "Public Housing" (1997) meets viewers' desires for authentic, unfiltered observation of marginalized communities, providing insight into the daily realities of residents in a Chicago housing project. It satisfies needs for social awareness and understanding of systemic poverty, offers a humanizing portrayal that challenges stereotypes, and appeals to those seeking cinema vérité's immersive, fly-on-the-wall documentary style that respects subjects' dignity while exploring complex social issues without narration or imposed commentary.</t>
         </is>
       </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7630,6 +7934,11 @@
 The film meets the desire for accessible, family-friendly content that both entertains and inspires without requiring cynicism or violence.</t>
         </is>
       </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7743,6 +8052,7 @@
 - **Emotional resonance** - taps into deep yearnings about purpose and human connection</t>
         </is>
       </c>
+      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7858,6 +8168,11 @@
 - **Cult cinema appreciation** for audiences who enjoy experimental, unconventional filmmaking
 - **Cultural pastiche** that plays with cinematic history and cross-cultural references
 The film primarily targets genre enthusiasts and Miike fans rather than mainstream audiences, meeting the need for bold, unconventional cinema that prioritizes style and audacity over traditional narrative coherence.</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7979,6 +8294,11 @@
 The film essentially meets needs for</t>
         </is>
       </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8096,6 +8416,11 @@
 The film appeals to audiences who enjoy psychological complexity, showbiz exposés, and stories about the relationship between art and exploitation.</t>
         </is>
       </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8217,6 +8542,11 @@
 The film satisfies audiences interested in artistic competition, romance, and classical music within a dramatic framework.</t>
         </is>
       </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8332,6 +8662,11 @@
 **Aesthetic pleasure** - Max Ophüls' elegant cinematography, elaborate tracking shots, and sumptuous period design offer visual sophistication and beauty. **Romantic tragedy** - The film delivers emotional depth through its portrayal of doomed love, sacrifice, and the painful consequences of deception. **Social commentary** - It provides insight into aristocratic society's superficiality, exploring themes of vanity, materialism, and how social codes constrain authentic emotion. **Intellectual engagement** - The circular narrative structure (centered on the earrings passing through different hands) and ironic storytelling invite viewers to appreciate craftsmanship and subtle symbolism. **Escapism with substance** - The glamorous Belle Époque setting offers escapism while maintaining psychological complexity and moral weight that elevates it beyond mere spectacle.</t>
         </is>
       </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8447,6 +8782,11 @@
 **Emotional catharsis** - The film provides an intense, sweeping romantic tragedy that allows audiences to experience profound love and loss vicariously. **Aesthetic pleasure** - Stunning cinematography, exotic locations, and lush production design satisfy desires for visual beauty and escapism. **Intellectual engagement** - The non-linear narrative and themes of identity, memory, and the costs of war appeal to viewers seeking complexity and depth. **Romantic fantasy** - The passionate, all-consuming love affair between Almásy and Katharine offers an idealized vision of romance. **Historical immersion** - The WWII setting and North African exploration provide context for those interested in period drama and history. **Multiple storylines** - Interwoven narratives satisfy viewers who appreciate layered storytelling and character studies examining how war affects different lives. The film essentially meets needs for both escapist romance and serious artistic cinema.</t>
         </is>
       </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8553,6 +8893,11 @@
 *The Girl with the Hat Box* (1927) meets viewers' desires for lighthearted romantic escapism, social commentary on housing shortages in 1920s Soviet Russia, and comedy through mistaken identities and class confusion. The film satisfies the need for optimistic entertainment that balances Soviet ideological messages with accessible, humorous storytelling about ordinary people navigating bureaucratic absurdities and finding love despite social obstacles.</t>
         </is>
       </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8666,6 +9011,11 @@
           <t>**The Heroic Trio** appeals to viewers seeking high-energy Hong Kong action cinema with stylized fight choreography, wire-fu spectacle, and superhero fantasy elements. It satisfies desires for strong female protagonists in traditionally male-dominated action roles, delivering campy entertainment with over-the-top villains, dystopian intrigue, and the visual flair characteristic of 1990s heroic bloodshed films. The movie meets needs for escapist fantasy, martial arts excitement, and cult film aesthetics.</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8773,6 +9123,11 @@
       <c r="W75" t="inlineStr">
         <is>
           <t>**The Holy Girl** meets viewers' desires for psychologically complex character studies and morally ambiguous narratives. It appeals to those interested in exploring themes of adolescent sexual awakening, religious guilt, obsession, and the blurred lines between devotion and desire. The film satisfies audiences seeking slow-paced, atmospheric cinema that prioritizes subtle emotional tension over conventional plot resolution, offering an unsettling examination of repression and manipulation within provincial Catholic culture.</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8885,6 +9240,11 @@
 - **Visual spectacle** through innovative silent film techniques and physical comedy
 - **Political validation** for Soviet audiences by critiquing bourgeois pretensions and celebrating working-class resilience
 The film balanced entertainment with ideological messaging, making it both enjoyable and politically appropriate for its time.</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9008,6 +9368,11 @@
 The film meets needs for both artistic appreciation and emotional engagement through its blend of gritty realism and romantic idealism.</t>
         </is>
       </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9095,6 +9460,7 @@
 **Intellectual stimulation** - The film explores complex Catholic theological debates and heresies throughout history, appealing to those interested in religious philosophy and doctrine. **Surrealist imagery** - Buñuel's signature dreamlike, absurdist sequences attract viewers who appreciate avant-garde cinema and non-linear storytelling. **Satirical critique** - The film meets the desire for irreverent examination of religious dogma and institutional authority, particularly appealing to skeptics and free-thinkers. **Historical exploration** - By depicting various theological controversies across centuries, it engages viewers curious about Church history and doctrinal development. **Artistic cinema** - The film satisfies cinephiles seeking challenging, unconventional narratives that prioritize ideas and symbolism over traditional plot structure.</t>
         </is>
       </c>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9203,6 +9569,11 @@
         <is>
           <t># Summary
 *The Most Terrible Time in My Life* (1994) meets viewers' desires for stylish neo-noir entertainment with its homage to classic detective films. The film satisfies audiences seeking atmospheric black-and-white cinematography, hard-boiled detective charm, and a blend of violence, mystery, and dark humor set in Yokohama's underworld. It appeals to fans of Japanese crime cinema who appreciate unconventional protagonists, gritty urban settings, and a mix of tension with offbeat comedic moments. The film also fulfills nostalgia for 1960s detective aesthetics while presenting a distinctly Japanese take on the genre.</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9298,6 +9669,11 @@
           <t>"The Outskirts of Alphaville" appeals to viewers seeking intellectual stimulation through experimental cinema that challenges conventional narrative structures. It meets desires for philosophical exploration of technology, surveillance, and dehumanization in modern society, while satisfying those interested in avant-garde aesthetics and dystopian themes. The film attracts cinephiles who appreciate references to Jean-Luc Godard's work and viewers drawn to meditative, visually striking examinations of urban alienation and the relationship between humanity and technological systems.</t>
         </is>
       </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9411,6 +9787,11 @@
           <t># The Player: Viewer Desires and Needs Met
 **The Player** (1992) satisfies several key viewer desires:
 **Insider Access**: Audiences get a satirical behind-the-scenes look at Hollywood's inner workings, revealing studio politics, deal-making, and creative compromises. **Schadenfreude**: Viewers enjoy watching morally compromised Hollywood executives exposed and satirized, particularly the narcissistic, self-serving studio system. **Mystery/Thriller Elements**: The murder plot provides suspense and narrative drive, keeping audiences engaged through traditional genre pleasures. **Intellectual Satisfaction**: The meta-cinematic elements, film references, and celebrity cameos reward knowledgeable viewers who appreciate self-reflexive commentary on moviemaking. **Dark Comedy**: The film delivers cynical humor about an industry that prioritizes commerce over art, appealing to those who enjoy biting social satire. **Moral Ambiguity**: The anti-hero protagonist challenges conventional morality, allowing viewers to explore ethical gray areas safely through fiction.</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9536,6 +9917,11 @@
 The film appeals to audiences seeking suspenseful, family-centered horror with accessible genre thrills.</t>
         </is>
       </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9645,6 +10031,11 @@
           <t>I don't have any information about a film called "The Stairway to the Distant Past" in my knowledge base. This title doesn't match any widely known or documented film I'm aware of. Without access to information about this specific work, I cannot describe what viewer desires or needs it might fulfill.</t>
         </is>
       </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9753,6 +10144,11 @@
         <is>
           <t># Summary
 *The Taking of Power by Louis XIV* meets viewers' desires for historical authenticity and intellectual engagement by depicting the strategic political maneuvering of the Sun King with documentary-like realism. The film satisfies interests in costume drama and visual spectacle through meticulous recreation of 17th-century court life, while appealing to those seeking cerebral, art-house cinema that explores themes of power, image-making, and the construction of authority through ritualized behavior and symbolic display.</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9861,6 +10257,11 @@
 The film appeals to audiences seeking thoughtful, character-driven narratives set against nature's beauty and brutality.</t>
         </is>
       </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9976,6 +10377,11 @@
 **Intellectual stimulation** - The film explores philosophical questions about fate, freedom, meaning, and the weight of our choices, adapted from Milan Kundera's novel. **Emotional complexity** - It presents morally ambiguous characters navigating love, commitment, and betrayal without easy answers, appealing to those who appreciate nuanced human drama. **Historical context** - Set against the 1968 Prague Spring and Soviet invasion, it fulfills interest in significant historical moments and political oppression. **Eroticism and intimacy** - The film features frank sexuality and explores the intersection of physical desire and emotional connection. **Artistic cinematography** - Beautiful visuals and sophisticated filmmaking attract cinephiles who value aesthetic craft. **Romantic complexity** - The unconventional love triangle between Tomas, Tereza, and Sabina appeals to viewers interested in non-traditional relationship dynamics and the nature of love versus desire.</t>
         </is>
       </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10081,6 +10487,11 @@
           <t># Summary of Viewer Needs Met by *The Wind Will Carry Us*
 Abbas Kiarostami's film satisfies viewers seeking:
 **Contemplative/Artistic Experience**: Slow cinema that rewards patience with philosophical depth about life, death, and human connection. **Intellectual Engagement**: Ambiguous narrative encouraging active interpretation rather than passive consumption. **Aesthetic Pleasure**: Stunning cinematography of Iranian village landscapes and poetic visual composition. **Cultural Insight**: Authentic portrayal of rural Iranian life, traditions, and rituals. **Existential Reflection**: Meditation on mortality, the exploitation of others' suffering, and finding meaning in everyday moments. **Anti-Commercial Alternative**: Escape from mainstream narrative conventions for audiences tired of formulaic storytelling.</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10194,6 +10605,7 @@
 The film satisfies audiences seeking challenging, politically radical cinema that deconstructs both narrative conventions and societal norms.</t>
         </is>
       </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10299,6 +10711,7 @@
           <t>"Xalé" (2018), a Senegalese film directed by Moussa Sène Absa, meets viewers' desires for authentic African storytelling, cultural exploration, and social commentary. The film addresses themes of youth, tradition versus modernity, family dynamics, and coming-of-age in contemporary Senegal. It appeals to audiences seeking diverse cinema, insight into West African culture, and narratives that explore generational conflicts and the challenges faced by young people navigating between traditional values and modern aspirations in a changing society.</t>
         </is>
       </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10382,6 +10795,7 @@
 - **Thought-provocation**: Complex narratives that challenge perspectives and spark reflection on contemporary issues</t>
         </is>
       </c>
+      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10504,6 +10918,11 @@
 The film provides both entertainment and validation for viewers' beliefs about justice, racial equality, and standing up against hatred.</t>
         </is>
       </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10615,6 +11034,11 @@
       <c r="W92" t="inlineStr">
         <is>
           <t>"GOAT" (2016) meets viewer desires for an intense, cautionary exploration of fraternity hazing culture. It appeals to audiences seeking realistic drama about toxic masculinity, peer pressure, and the psychological toll of seeking acceptance through brutal initiation rituals. The film satisfies those interested in thought-provoking social commentary on American college life, masculine identity, and the dark side of brotherhood traditions, while also providing visceral tension and emotional depth for viewers who appreciate character-driven indie cinema that challenges institutional norms.</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10734,6 +11158,11 @@
 - **Philosophical exploration** of immortality, desire, and spiritual conflict</t>
         </is>
       </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10845,6 +11274,11 @@
       <c r="W94" t="inlineStr">
         <is>
           <t>"Good Luck, Have Fun, Don't Die" is a documentary about competitive gaming (esports) that meets viewer desires for understanding gaming culture, following underdog stories and personal journeys of professional gamers, experiencing the intensity of high-stakes competition, and gaining insight into a subculture that bridges digital and real-world achievement. It appeals to both gaming enthusiasts seeking validation of their passion and general audiences curious about the emerging world of professional esports.</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10961,6 +11395,7 @@
 The film satisfies niche audiences interested in experimental narratives that challenge conventional boundaries between life and death, love and obsession.</t>
         </is>
       </c>
+      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11079,6 +11514,11 @@
 The film primarily appeals to viewers wanting intellectually challenging, artistically ambitious horror-thriller experiences that push boundaries.</t>
         </is>
       </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11188,6 +11628,11 @@
           <t>I don't have any information about a film called "Pillion" in my knowledge base. Without knowing the film's content, themes, or context, I cannot accurately describe what viewer desires or needs it might meet.</t>
         </is>
       </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11301,6 +11746,11 @@
           <t>I don't have information about Scream 7, as it hasn't been released yet and I don't have access to current information beyond April 2024. At that time, Scream 7 was in early development with no release date or confirmed plot details available.</t>
         </is>
       </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11414,6 +11864,11 @@
           <t>"Send Help" is a dark comedy that meets viewers' desires for satirical entertainment about influencer culture and social media obsession. It appeals to audiences seeking humor in the absurdity of online personas, the disconnect between curated digital lives and reality, and commentary on modern communication breakdowns. The film satisfies needs for both escapist comedy and social critique of contemporary digital lifestyle trends.</t>
         </is>
       </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11523,6 +11978,11 @@
           <t>I don't have specific information about a film called "Sirāt" in my knowledge base. Without details about this particular film's content, themes, or context, I cannot accurately describe what viewer desires or needs it meets. If you could provide more information about the film (such as the director, year, or country of origin), I might be able to offer a more helpful response.</t>
         </is>
       </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11636,6 +12096,11 @@
           <t>"Wuthering Heights" meets viewers' desires for intense romantic passion, gothic atmosphere, and exploration of dark human emotions like obsession, revenge, and destructive love. It appeals to those seeking tragic romance, complex morally ambiguous characters, class conflict drama, and the cathartic experience of witnessing love that transcends death and social boundaries, all set against the wild, atmospheric Yorkshire moors that mirror the characters' turbulent emotions.</t>
         </is>
       </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11749,6 +12214,11 @@
           <t>"Birth" meets viewers' desires for psychological complexity and ambiguity, exploring themes of grief, obsession, and the irrational nature of belief. It appeals to those who appreciate slow-burn tension, atmospheric filmmaking, and morally ambiguous narratives that resist easy answers. The film satisfies audiences seeking mature, unsettling examinations of love, loss, and the lengths people go to hold onto the past, while offering Nicole Kidman's nuanced performance and Jonathan Glazer's precise, haunting visual style.</t>
         </is>
       </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11856,6 +12326,11 @@
       <c r="W103" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "Brand X" in my knowledge base. Without knowing the specific film you're referring to (as there may be multiple works with this title across different years and media), I cannot accurately describe what viewer desires or needs it meets. If you could provide more context such as the release year, director, or genre, I would be better able to help.</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11955,6 +12430,7 @@
           <t>The film "Earth" (1998) by Deepa Mehta meets viewers' desires for emotionally powerful storytelling about Partition, exploring themes of religious conflict, lost innocence, and forbidden love through a child's perspective. It satisfies needs for historical understanding of India-Pakistan division while delivering compelling human drama, complex characters, and a critique of communal violence that resonates with audiences seeking both personal stories and broader sociopolitical commentary.</t>
         </is>
       </c>
+      <c r="X104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12068,6 +12544,11 @@
           <t># Summary: Viewer Desires Met by L'Eclisse
 **L'Eclisse** (1962) fulfills several artistic and intellectual viewer needs:
 **Aesthetic appreciation**: Antonioni's stunning visual composition and cinematography satisfy viewers seeking pure cinematic beauty and architectural imagery. **Intellectual engagement**: The film rewards those interested in existential themes, examining modern alienation, emotional disconnection, and the difficulty of authentic human connection in contemporary society. **Emotional ambiguity**: It appeals to viewers comfortable with unresolved narratives and ambiguous endings, offering space for personal interpretation rather than conventional closure. **Atmospheric experience**: The film provides a meditative, mood-driven experience for audiences who appreciate cinema as experiential art rather than plot-driven entertainment. **Cultural sophistication**: It satisfies the desire for European art cinema that challenges mainstream conventions and demonstrates high cultural literacy.</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12153,6 +12634,7 @@
 **Intellectual stimulation** - It offers a contemplative exploration of faith, doubt, and existential questions through minimal dialogue and observational storytelling. **Artistic/aesthetic appreciation** - The film's slow-cinema approach and visual storytelling appeal to those seeking cinematic artistry over conventional narrative. **Emotional reflection** - It provides space for viewers to project their own experiences with spirituality, family dynamics, and personal crisis. **Alternative perspectives** - The film satisfies curiosity about religious practice and belief in contemporary Argentina, particularly regarding Jewish identity and tradition. **Contemplative experience** - For patient viewers, it offers a meditative viewing experience that contrasts with mainstream entertainment's faster pace.</t>
         </is>
       </c>
+      <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12246,6 +12728,11 @@
           <t>I don't have enough information to provide an accurate answer about a film called "Screen." There are multiple films with this title or similar names from different years and countries. Without knowing which specific film you're referring to (director, year, or other identifying details), I cannot reliably describe what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12353,6 +12840,11 @@
       <c r="W108" t="inlineStr">
         <is>
           <t>I don't have enough information to provide an accurate answer about a film called "Sky." There are multiple films with this title from different years and countries. Without knowing which specific film you're referring to (director, year, or other identifying details), I cannot reliably describe what viewer desires or needs it addresses.</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12463,6 +12955,11 @@
 **Poetic/philosophical reflection** - narrated in Alexandrine verse by Raymond Queneau, elevating mundane manufacturing into meditation on transformation and creation
 **Formal innovation** - satisfying cinephiles interested in experimental documentary techniques that blend art, industry, and poetry
 **Modernist fascination** - celebrating post-war technological progress and industrial aesthetics popular in 1950s French culture</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12562,6 +13059,11 @@
 - **Intimate, observational storytelling** - provides quiet, character-focused narrative that feels like witnessing something real and private</t>
         </is>
       </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12651,6 +13153,11 @@
           <t>The 2019 Oscar Nominated Shorts: Animation meets viewers' desires for artistic innovation, diverse storytelling, and emotional depth in compact formats. It satisfies curiosity about award-worthy cinema, offers exposure to international perspectives and animation techniques, and provides an efficient way to experience multiple acclaimed films in one sitting. The collection appeals to animation enthusiasts, film students, and audiences seeking thoughtful, visually striking narratives that range from whimsical to profound.</t>
         </is>
       </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -12764,6 +13271,11 @@
           <t># Days of Being Wild: Viewer Desires and Needs Met
 Wong Kar-wai's **Days of Being Wild** (1990) satisfies several key viewer desires:
 **Aesthetic Pleasure**: The film delivers stunning cinematography, lush colors, and atmospheric visuals that create a dreamlike, nostalgic mood. **Emotional Resonance**: It explores universal themes of loneliness, unfulfilled longing, and the search for identity, allowing viewers to connect with characters' emotional struggles. **Atmospheric Immersion**: The film's languorous pacing and evocative 1960s Hong Kong setting provide an immersive, meditative experience that transports viewers to another time and place. **Art Cinema Appreciation**: It meets the needs of viewers seeking sophisticated, non-linear storytelling and character-driven narratives that prioritize mood and psychology over plot. **Romantic Melancholy**: The film appeals to those drawn to bittersweet romance and the beauty of transient, unfulfilled relationships.</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12875,6 +13387,11 @@
 The film appeals to viewers seeking sophisticated, emotionally complex cinema that doesn't shy away from the messiness of human relationships.</t>
         </is>
       </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12976,6 +13493,11 @@
           <t>National Theatre Live: People meets viewers' desires for witty, intelligent theatre that explores themes of class, heritage, and social responsibility. The film satisfies audiences seeking sharp British comedy-drama featuring strong performances, particularly from older female leads. It appeals to those interested in debates about preserving historic estates versus social welfare, offering both entertainment and thought-provoking commentary on contemporary British society. The National Theatre Live format also serves viewers who want access to high-quality stage productions without attending in person.</t>
         </is>
       </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13077,6 +13599,7 @@
           <t>I don't have any information about a film called "Skin of Youth" in my knowledge base. This could be a lesser-known, independent, or recent film that I'm not familiar with, or it may be known by a different title. Without access to details about this specific film, I cannot provide an accurate summary of what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13190,6 +13713,11 @@
           <t>I don't have specific information about a film called "The Moment" to provide an accurate summary of what viewer desires or needs it meets. There are multiple films with this title from different years and countries, and without knowing which specific film you're referring to, I cannot give you a reliable answer about its themes or audience appeal.</t>
         </is>
       </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13303,6 +13831,11 @@
           <t>"Wuthering Heights" meets viewers' desires for intense romantic passion, exploration of dark and obsessive love, class conflict drama, and Gothic atmosphere. It appeals to those seeking emotional catharsis through tragic storytelling, examining themes of revenge, social barriers, and the destructive power of unrequited love. The film satisfies audiences interested in period drama, complex antiheroes, and narratives that explore how childhood trauma and social injustice shape human behavior across generations.</t>
         </is>
       </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13405,6 +13938,11 @@
 *Criadas* (The Maids) meets viewer desires for psychological tension, class conflict drama, and intimate character studies. The film satisfies audiences seeking exploration of power dynamics, repressed desires, and social inequality through its portrayal of domestic workers and their employers. It appeals to those interested in chamber pieces with theatrical intensity, feminist themes, and examinations of servitude and rebellion. The film also attracts viewers drawn to adaptations of Jean Genet's provocative work and Spanish-language arthouse cinema that challenges conventional narratives about labor and identity.</t>
         </is>
       </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13516,6 +14054,11 @@
       <c r="W119" t="inlineStr">
         <is>
           <t>"Far from Heaven" meets viewers' desires for emotionally complex melodrama, nostalgic 1950s aesthetics, and thoughtful exploration of repressed social issues including racism, homophobia, and gender constraints. The film satisfies needs for both visual beauty through its Sirkian Technicolor style and substantive commentary on the gap between idealized suburban perfection and painful personal truths. It appeals to audiences seeking sophisticated adult drama that honors classic Hollywood while offering modern progressive perspectives on forbidden love and social conformity.</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13611,6 +14154,7 @@
 The film resonates with both surfing insiders who identify with territorial protection of home breaks and outsiders curious about this often-exclusionary aspect of surf culture.</t>
         </is>
       </c>
+      <c r="X120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -13714,6 +14258,11 @@
       <c r="W121" t="inlineStr">
         <is>
           <t>"Manas" (1991) is a Kyrgyz epic film that meets viewers' desires for cultural identity, national pride, and connection to their heritage. It satisfies the need to see their own traditional stories and values represented on screen, particularly the famous Epic of Manas that is central to Kyrgyz culture. The film appeals to audiences seeking historical drama, heroic storytelling, and preservation of oral traditions in cinematic form. It also fulfills desires for epic adventure narratives featuring themes of courage, leadership, and the struggle for freedom and unity.</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13831,6 +14380,11 @@
 The film caters to adult audiences comfortable with graphic sexuality and violence, who appreciate slow-burn tension and visual storytelling over conventional narrative structure.</t>
         </is>
       </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13936,6 +14490,11 @@
           <t>"O Último Episódio" (The Last Episode) is a 2016 Brazilian documentary that meets viewers' desires for nostalgic reflection on television history and cultural memory. It appeals to audiences interested in understanding Brazil's relationship with telenovelas (soap operas) and their profound cultural impact. The film satisfies needs for thoughtful examination of how serialized storytelling shapes collective identity, provides emotional connection to shared viewing experiences, and explores themes of endings, memory, and the evolution of media consumption in Brazilian society.</t>
         </is>
       </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14047,6 +14606,11 @@
       <c r="W124" t="inlineStr">
         <is>
           <t>"Safe" (1995) meets viewers' desires for psychological horror that explores modern anxieties about environmental illness, alienation, and loss of control. It satisfies those seeking ambiguous, unsettling cinema that critiques both toxic modernity and false wellness solutions, offering no easy answers while creating profound unease about the fragility of selfhood and the isolating nature of unexplained suffering.</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14158,6 +14722,11 @@
 The film satisfies audiences wanting an uplifting, accessible adventure suitable for all ages.</t>
         </is>
       </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14247,6 +14816,7 @@
           <t>"Beyond the Berlin Wall: Reports from Stasi Prisoners" meets viewers' desires for historical truth and justice by documenting the experiences of political prisoners under East Germany's secret police. The film satisfies needs for understanding authoritarian oppression, preserving testimony from victims of state surveillance and abuse, and learning about Cold War-era human rights violations. It appeals to those seeking educational content about totalitarian regimes and the human cost of political repression.</t>
         </is>
       </c>
+      <c r="X126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14368,6 +14938,11 @@
 The film combines horror entertainment with emotionally resonant themes about childhood trauma, making it both frightening and meaningful.</t>
         </is>
       </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14481,6 +15056,11 @@
           <t>Serial Mom satisfies viewers' desires for dark comedy, satirical social commentary, and cathartic revenge fantasies. The film appeals to audiences who enjoy subversive humor that mocks suburban conformity, celebrates rule-breaking, and finds comedy in taboo subjects like murder. It provides entertainment through over-the-top violence paired with absurdist humor, while offering a critique of media sensationalism and middle-class hypocrisy. The film also delivers camp appeal and transgressive fun for fans of John Waters' deliberately provocative style.</t>
         </is>
       </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14582,6 +15162,11 @@
           <t>I don't have specific information about a film called "To Be Free" in my knowledge base. There could be multiple films with this or similar titles. Without knowing which specific film you're referring to or having details about its content, I cannot accurately describe what viewer desires or needs it meets. If you could provide additional context such as the year of release, director, or subject matter, I might be able to help you better.</t>
         </is>
       </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14694,6 +15279,11 @@
         <is>
           <t># Summary of Viewer Desires Met by "Sinners"
 "Sinners" appeals to audiences seeking stylish supernatural horror with strong performances, particularly fans of vampires and period settings. It satisfies desires for atmospheric tension, genre thrills, and compelling lead actors (notably Michael B. Jordan in dual roles). The film attracts viewers interested in African American narratives within horror, as well as those who appreciate visually striking cinematography and moody Southern Gothic aesthetics. It meets needs for escapist entertainment that blends action, horror elements, and dramatic storytelling.</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14819,6 +15409,11 @@
 The film essentially meets the need for lighthearted, non-demanding entertainment that doesn't take itself seriously.</t>
         </is>
       </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14930,6 +15525,11 @@
       <c r="W132" t="inlineStr">
         <is>
           <t>The film *Chicago* meets viewers' desires for spectacular entertainment, escapism, and glamorous fantasy through its dazzling musical numbers and stylized choreography. It satisfies the need for moral complexity by presenting morally ambiguous antiheroes while critiquing celebrity culture, media manipulation, and the corruption of justice. The film also appeals to desires for empowerment through its strong female leads who pursue their ambitions unapologetically, offers cathartic emotional release through its blend of dark comedy and drama, and provides visual and auditory pleasure through its innovative staging, costuming, and jazzy musical score.</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15053,6 +15653,11 @@
 7. **Representation** - offering Latino/Mexican cultural visibility in mainstream cinema</t>
         </is>
       </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15165,6 +15770,11 @@
         <is>
           <t># Viewer Desires Met by Ghidorah, the Three-Headed Monster
 The film satisfies multiple audience needs: **escapism and spectacle** through massive monster battles and special effects, **wish fulfillment** via the fantasy of giant creatures defending humanity, **tension and release** through disaster scenarios resolved heroically, **nostalgia** for kaiju genre conventions, and **morality play comfort** with clear good vs. evil conflicts. It also provides **communal viewing pleasure** in shared excitement over iconic monster showdowns, particularly Godzilla's transformation from villain to hero alongside Rodan and Mothra against the alien threat.</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15284,6 +15894,11 @@
 The film ultimately serves as crowd-pleasing horror entertainment that validates traditional values while delivering Gothic thrills.</t>
         </is>
       </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -15381,6 +15996,7 @@
           <t>I don't have any information about a film called "Possum Town" in my knowledge base. Without details about this specific film, I cannot accurately describe what viewer desires or needs it meets. This may be an obscure, independent, or regional film, or possibly a very recent release that falls outside my training data.</t>
         </is>
       </c>
+      <c r="X136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -15504,6 +16120,11 @@
 The film became a cultural phenomenon by creating a safe, celebratory space for marginalized identities and rebellious self-expression.</t>
         </is>
       </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15593,6 +16214,11 @@
           <t>The 2019 Oscar Nominated Shorts: Animation meets viewers' desires for creative storytelling, artistic diversity, and exposure to international cinema in a compact format. It satisfies curiosity about award-contending work, offers emotional and thought-provoking narratives, and provides an accessible way to experience cutting-edge animation techniques and varied visual styles from around the world—all within a single theatrical program that validates viewers' interest in prestige content and cultural literacy.</t>
         </is>
       </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15706,6 +16332,11 @@
           <t>I don't have any information about "28 Years Later: The Bone Temple." This film doesn't appear in my knowledge base, which has a training cutoff date in April 2024. If this is a recently announced or released film, I wouldn't have details about it yet.</t>
         </is>
       </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15817,6 +16448,11 @@
       <c r="W140" t="inlineStr">
         <is>
           <t>"How to Make a Killing" appeals to viewers interested in dark comedy and satirical takes on corporate greed and capitalism. The film meets desires for cynical humor, social commentary on business ethics, and entertainment that critiques materialistic culture. It attracts audiences who enjoy morally ambiguous characters and stories that expose the absurdities of profit-driven behavior.</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15938,6 +16574,11 @@
 - **Cultural representation** - Hawaiian culture and setting provide authenticity and diversity often lacking in mainstream animation
 - **Found family themes** - The unconventional family structure validates that family isn't always traditional
 - **Nostalgia and comfort** - The film offers a warm, ultimately hopeful story that provides emotional reassurance</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -16063,6 +16704,11 @@
 The film delivers sophisticated thriller entertainment that engages both mind and adrenaline.</t>
         </is>
       </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16184,6 +16830,11 @@
 The film appeals to viewers who enjoy improvised comedy, experimental formats, and authentic creative expression over polished production.</t>
         </is>
       </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -16305,6 +16956,11 @@
 7. **Countercultural identity** - Allows viewers to express rebellion against conservative values and embrace non-conformity</t>
         </is>
       </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -16416,6 +17072,11 @@
       <c r="W145" t="inlineStr">
         <is>
           <t>"Wuthering Heights" meets viewers' desires for intense romantic passion, dramatic emotional conflict, and Gothic atmosphere. It appeals to those drawn to tragic love stories, complex characters driven by obsession and revenge, exploration of class divisions, and the dark side of human nature. The film satisfies audiences seeking powerful performances, brooding atmosphere, and timeless themes of love's destructive potential and the consequences of social constraints on personal desire.</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -16512,6 +17173,11 @@
 5. **Efficient entertainment** - Offering varied storytelling experiences in a single screening
 6. **Creative inspiration** - Demonstrating the storytelling potential of short-form animation
 The compilation satisfies both casual animation fans and serious cinephiles seeking quality, thought-provoking content.</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -16591,6 +17257,7 @@
           <t>"2020 SLAMMY Award Winners" meets viewers' desires for entertainment through wrestling-related content, recognition of achievements in the wrestling community, and nostalgia for award show formats. It satisfies fans' needs to celebrate their favorite performers, see highlight moments from the year, and engage with wrestling culture beyond regular matches.</t>
         </is>
       </c>
+      <c r="X147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -16702,6 +17369,11 @@
       <c r="W148" t="inlineStr">
         <is>
           <t>"A New Leaf" satisfies viewers' desires for sharp wit and romantic comedy with a dark edge. It appeals to those who enjoy watching a character transform from selfish narcissist to someone capable of love, offers the pleasure of seeing Elaine May's endearing portrayal of an awkward but genuine person triumph over cynicism, and provides both sophisticated verbal comedy and physical humor. The film meets needs for intelligent entertainment that doesn't follow conventional rom-com formulas while still delivering warmth and charm.</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -16824,6 +17496,11 @@
 The film primarily serves viewers seeking intense sensory experiences and transgressive content rather than narrative sophistication.</t>
         </is>
       </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -16938,6 +17615,11 @@
 - **Justice and retribution** - The protagonist's quest to protect his family and settle old scores fulfills the desire to see wrongs corrected
 - **Suspense and danger** - Criminal threats and violent confrontations deliver tension and excitement
 - **1970s Euro-crime atmosphere** - Provides the stylistic appeal of European action cinema from that era</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -17061,6 +17743,11 @@
 The film serves viewers who value challenging, boundary-pushing cinema over entertainment, offering validation for difficult feelings about parenthood and domestic life rarely depicted on screen.</t>
         </is>
       </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -17182,6 +17869,11 @@
 The film satisfies audiences drawn to prestige literary adaptations and character-driven historical dramas that explore the human cost behind great artistic achievement.</t>
         </is>
       </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -17287,6 +17979,11 @@
           <t>I don't have enough information to provide an accurate answer about a film called "Interior" as there are multiple films with this title from different years and directors. Without knowing which specific film you're referring to (director, year, or additional context), I cannot reliably describe what viewer desires or needs it fulfills.</t>
         </is>
       </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -17388,6 +18085,11 @@
           <t>I don't have any information about a film called "My Degeneration" in my knowledge base. This title doesn't match any widely known documentary or feature film I'm aware of. You may be thinking of a different title, or this could be an obscure or independent film not well-documented in available sources.</t>
         </is>
       </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -17497,6 +18199,11 @@
           <t>I don't have any information about a film called "Numbskull Revolution" in my knowledge base. This title doesn't appear to correspond to any widely known or documented film that I'm aware of. Without access to information about this specific work, I cannot provide a summary of what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -17592,6 +18299,11 @@
 **Time Efficiency**: They respect busy schedules by delivering complete stories in minutes rather than hours, perfect for modern attention spans and fragmented viewing habits. **Creative Experimentation**: Viewers seeking artistic innovation appreciate short films' freedom to take risks with unconventional narratives, visual styles, and experimental techniques that mainstream features often avoid. **Accessibility**: They provide entry points for discovering new filmmakers, voices, and perspectives without significant time investment, making them ideal for film festivals and online platforms. **Concentrated Impact**: Short films deliver focused emotional or intellectual experiences without the commitment of feature-length viewing, offering quick satisfaction and thought-provocation. **Diverse Storytelling**: They meet the desire for variety, allowing viewers to experience multiple complete narratives, genres, and styles in a single viewing session.</t>
         </is>
       </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -17705,6 +18417,11 @@
           <t>I don't have specific information about a film called "Seeds" in my knowledge base. There are multiple films with this title from different years and genres.</t>
         </is>
       </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -17818,6 +18535,11 @@
           <t>"The Day of the Beast" meets viewers' desires for darkly comedic horror that subverts religious themes, combining shock value with satirical social commentary. It appeals to those seeking transgressive, unconventional cinema that blends blasphemous humor with genuine suspense, while offering a unique Spanish perspective on apocalyptic narratives. The film satisfies fans of cult cinema who appreciate irreverent takes on good versus evil, extreme situations played for both laughs and thrills, and visually striking urban chaos.</t>
         </is>
       </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -17915,6 +18637,7 @@
           <t>I don't have any information about a film called "Now Playing" in my knowledge base. This title may refer to a lesser-known or independent film, or it could be a generic phrase used by theaters to indicate current screenings. Without specific details about this particular film, I cannot provide an accurate summary of what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -18000,6 +18723,7 @@
           <t>The 2018 Oscar Nominated Short Films: Documentary collection meets viewers' desires for impactful, concise storytelling that explores diverse human experiences and social issues. It satisfies the need for thought-provoking content that can be consumed in shorter time frames, offers exposure to award-caliber filmmaking, and provides insight into important real-world topics ranging from humanitarian crises to personal struggles. The compilation format also appeals to viewers interested in the Oscar race and those seeking to engage with critically acclaimed documentary work without committing to feature-length films.</t>
         </is>
       </c>
+      <c r="X160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -18109,6 +18833,11 @@
           <t>"A New Love in Tokyo" (1994) meets viewer desires for romantic escapism and cultural exploration. The film appeals to audiences seeking a nostalgic portrayal of Tokyo's urban romance, offering emotional connection through its love story while satisfying curiosity about Japanese culture and city life. It provides entertainment through its blend of drama and romance, allowing viewers to experience vicarious emotional journeys and the excitement of cross-cultural relationships in an exotic setting.</t>
         </is>
       </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -18218,6 +18947,11 @@
           <t>"Abnormal Family" (1984), a Japanese pink film directed by Masayuki Suo, appeals to viewers seeking transgressive adult content that explores taboo sexual themes within a family context. The film meets desires for provocative, boundary-pushing erotic cinema that confronts social norms around sexuality and family dynamics, typical of the pink film genre which blends explicit content with artistic or satirical social commentary.</t>
         </is>
       </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -18315,6 +19049,11 @@
           <t>The film meets viewers' desires for an inspiring story of musical talent and spiritual redemption, offering insight into Billy Preston's remarkable career as a legendary keyboardist who collaborated with The Beatles and other icons, while also addressing his personal struggles. It satisfies needs for understanding his cultural impact, celebrating his contributions to music history, and experiencing the intersection of gospel, soul, and rock through the lens of an underappreciated artist's life journey.</t>
         </is>
       </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -18430,6 +19169,11 @@
 **Escapism and Exotic Beauty**: The film transports audiences to the vibrant Rio Carnival with stunning cinematography, colorful costumes, and the sensual rhythms of bossa nova, offering an immersive escape into Brazilian culture. **Romantic Tragedy**: It fulfills the need for emotional catharsis through its retelling of the Orpheus and Eurydice myth as a doomed love story, providing the pleasurable sadness of tragic romance. **Cultural Discovery**: Viewers experience authentic Afro-Brazilian culture, music, and favela life, satisfying curiosity about a then-unfamiliar world while celebrating Black beauty and artistry. **Universal Themes**: By adapting Greek mythology to a contemporary setting, it meets the desire for timeless stories about love, fate, and loss that transcend cultural boundaries. **Aesthetic Pleasure**: The film's visual poetry, Dance sequences, and iconic soundtrack (particularly "Manhã de Carnaval") provide pure sensory enjoyment and have lasting cultural appeal</t>
         </is>
       </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -18541,6 +19285,11 @@
 1. **Representation and inclusivity** - It centers deaf characters and incorporates American Sign Language authentically, fulfilling the need for disability representation in cinema. 2. **Artistic innovation** - The parallel silent film/modern film structure appeals to cinephiles interested in experimental storytelling and film history. 3. **Romantic storytelling** - It provides an emotionally resonant love story that transcends communication barriers. 4. **Cultural authenticity** - The film addresses deaf culture and community experiences, meeting the need for accurate cultural portrayals. 5. **Visual poetry** - Its lyrical, image-driven narrative satisfies viewers seeking contemplative, aesthetically beautiful cinema over conventional plot-driven films.</t>
         </is>
       </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -18648,6 +19397,11 @@
       <c r="W166" t="inlineStr">
         <is>
           <t>"In the Hand of Dante" meets viewer desires for literary adaptation, exploration of Dante's classic work through a modern lens, meta-fictional storytelling that blends past and present narratives, and philosophical contemplation about art, mortality, and redemption. The film appeals to audiences interested in intellectual cinema, Oscar Isaac's performance, and unconventional narrative structures that challenge traditional filmmaking approaches.</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -18767,6 +19521,11 @@
 The film satisfies audiences who enjoy thought-provoking, contemplative science fiction similar to works like "Moon" or "2001: A Space Odyssey," though on a much smaller scale.</t>
         </is>
       </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -18872,6 +19631,11 @@
           <t>"Riverbend" (1989) is an action thriller that meets viewer desires for revenge-driven narratives, depicting a Vietnam veteran who battles corrupt small-town officials after being falsely imprisoned. The film satisfies audiences seeking vigilante justice, underdog triumph stories, and action-packed confrontations against systemic corruption, while also appealing to fans of 1980s exploitation cinema with its combination of violence, survival elements, and a wronged hero fighting back against abuse of power.</t>
         </is>
       </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -18981,6 +19745,11 @@
           <t>"Shuffle" (2011) meets viewers' desires for thought-provoking drama about mortality, family, and the meaning of life. The film's unique premise—following a man experiencing his life's days in random order—appeals to audiences seeking non-linear storytelling, philosophical exploration of time and memory, and emotional reflection on how we value our relationships and moments. It satisfies the need for introspective cinema that challenges conventional narrative structure while delivering poignant messages about appreciating life.</t>
         </is>
       </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -19090,6 +19859,11 @@
           <t>"Sirāt" (2024) is a Moroccan drama that meets viewers' desires for authentic cultural storytelling, exploring themes of faith, morality, and personal redemption within an Islamic framework. The film appeals to audiences seeking meaningful narratives about spiritual struggle, the tension between traditional values and modern life, and the complexities of navigating one's path (sirāt means "the path" in Arabic) in contemporary society. It satisfies needs for representation of North African Muslim experiences and contemplative cinema that engages with existential questions.</t>
         </is>
       </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -19201,6 +19975,11 @@
       <c r="W171" t="inlineStr">
         <is>
           <t>"Somersault" meets viewers' desires for emotionally authentic coming-of-age storytelling, exploring themes of sexual awakening, self-discovery, and isolation through visually poetic cinematography. The film appeals to audiences seeking intimate character studies of vulnerability and identity formation, particularly resonating with those who appreciate slow-paced, atmospheric Australian cinema that prioritizes mood and emotional truth over plot-driven narrative.</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -19320,6 +20099,11 @@
 The film meets the fundamental need to experience transcendent live performance while showcasing Talking Heads at their creative peak.</t>
         </is>
       </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -19417,6 +20201,7 @@
           <t>"The Man Who Saves the World" (1982), also known as "Turkish Star Wars," meets viewer desires for campy entertainment, cult film appreciation, and so-bad-it's-good cinema. The film appeals to audiences who enjoy absurdist humor, low-budget filmmaking curiosities, bizarre cultural mashups (it notoriously uses stolen footage from Star Wars), and the experience of watching gloriously chaotic, unintentionally comedic movies. It satisfies needs for ironic enjoyment, cultural oddities, and shared communal laughter at outrageous cinema.</t>
         </is>
       </c>
+      <c r="X173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -19528,6 +20313,11 @@
 **Aesthetic/Sensory Appeal**: The film satisfies desires for visual beauty through its stunning cinematography, elaborate body calligraphy, and innovative layered screen compositions that create a painterly, artistic experience. **Intellectual Engagement**: It appeals to viewers seeking cerebral content through its exploration of Eastern philosophy, literature (referencing Sei Shōnagon's classical text), and themes of language, writing, and cultural identity. **Erotic Interest**: The film fulfills desires for sensual content through its explicit depiction of sexuality intertwined with art, presenting the body as canvas and exploring intimate human connection. **Narrative Complexity**: It satisfies viewers who enjoy non-linear storytelling and experimental narrative structures that challenge conventional filmmaking. **Cultural Exploration**: The film meets curiosity about Japanese culture, aesthetics, and the fusion of Eastern and Western artistic traditions. **Emotional Catharsis**: It provides emotional depth through themes of revenge, love, loss, and personal transformation, offering viewers a complex emotional journey.</t>
         </is>
       </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -19629,6 +20419,11 @@
           <t>"The Puffy Chair" meets viewers' desires for authentic, relatable relationship stories and intimate character studies. It appeals to those seeking low-budget indie filmmaking that captures genuine emotional conflicts, particularly around commitment issues and family dynamics in young adulthood. The film satisfies audiences interested in naturalistic dialogue, improvised performances, and the mumblecore aesthetic that prioritizes realism over polish. It also connects with viewers navigating their own relationship uncertainties and the complexities of balancing romance with personal identity.</t>
         </is>
       </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -19734,6 +20529,11 @@
           <t># The Razor's Edge - Viewer Desires and Needs Met
 **The Razor's Edge** appeals to viewers seeking:
 - **Spiritual exploration and meaning** - The film follows a protagonist's quest for enlightenment and life's deeper purpose, resonating with those questioning materialism and searching for transcendence. - **Escape from convention** - It validates the desire to reject societal expectations of success, career, and wealth in favor of personal truth and authenticity. - **Philosophical contemplation** - Viewers interested in existential questions about suffering, happiness, and the nature of fulfillment find intellectual stimulation. - **Vicarious transformation** - The journey from disillusioned war veteran to enlightened seeker offers hope that profound personal change is possible. - **Critique of materialism** - It satisfies the need to see wealthy, superficial lifestyles challenged and ultimately found wanting compared to spiritual richness.</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -19849,6 +20649,11 @@
 The film appeals to art-house audiences seeking cinema as a contemplative, humanistic art form rather than pure entertainment.</t>
         </is>
       </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -19966,6 +20771,11 @@
 The film meets needs for both artistic appreciation and genre entertainment, making it enduringly popular with serious film enthusiasts.</t>
         </is>
       </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -20082,6 +20892,11 @@
 - **Existential validation** - It celebrates the value of ordinary human experiences—feeling, touching, tasting—that might otherwise seem mundane</t>
         </is>
       </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -20193,6 +21008,11 @@
       <c r="W180" t="inlineStr">
         <is>
           <t>"Iced" (1988) is a slasher film that appeals to horror fans seeking straightforward revenge-driven kills, 1980s nostalgia, ski resort settings, and B-movie entertainment. It satisfies desires for genre thrills, gratuitous violence, sexual content typical of the era, and the formulaic pleasure of watching characters meet gruesome fates in an isolated location.</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -20315,6 +21135,11 @@
 - **Cult film experience**: Satisfies the desire to engage with challenging, divisive cinema that rewards repeat viewings and interpretation</t>
         </is>
       </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -20421,6 +21246,11 @@
 *Alma's Rainbow* (1994) meets viewers' desires for authentic Black women's stories by focusing on three generations navigating identity, colorism, beauty standards, and sexuality within their community. The film addresses needs for representation of African American family dynamics, coming-of-age experiences, and intergenerational relationships rarely seen in mainstream cinema. It also fulfills desires for independent, woman-centered narratives that explore cultural pride, self-acceptance, and the complexities of mother-daughter relationships without male-dominated storylines.</t>
         </is>
       </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -20519,6 +21349,7 @@
 *Nothing but Time* (1926), a French avant-garde documentary by Alberto Cavalcanti, meets viewer desires for artistic innovation and social consciousness. The film satisfies interests in experimental cinema through its modernist techniques (rhythmic editing, unusual camera angles, superimpositions), while documenting Parisian working-class life and celebrating industrial labor. It appeals to audiences seeking both aesthetic novelty and authentic portrayals of everyday people, fulfilling desires for films that are simultaneously artistically bold and socially relevant. The poetic depiction of urban rhythms and human dignity in industrial settings resonates with viewers interested in city symphonies and humanistic documentary approaches.</t>
         </is>
       </c>
+      <c r="X183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -20612,6 +21443,11 @@
           <t>"Stories Our Nannies Don't Tell" meets viewers' desires for understanding the hidden experiences of domestic workers, particularly Caribbean nannies in Canada. The film satisfies needs for social awareness about labor inequality, immigration challenges, and the emotional costs of caregiving work. It appeals to audiences seeking authentic narratives about marginalized communities, family separation, and the complex power dynamics between employers and domestic workers, while also fulfilling desires for empathy-building and social justice content.</t>
         </is>
       </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -20722,6 +21558,11 @@
 *The Spook Who Sat by the Door* (1973) meets viewer desires for revolutionary Black empowerment narratives and critiques of systemic racism. It appeals to audiences seeking authentic portrayals of Black resistance, political awakening, and subversive commentary on American institutions. The film satisfies needs for representation that challenges mainstream narratives, offering a provocative exploration of racial inequality, tokenism, and revolutionary action that resonated particularly with Black audiences during the Black Power era and continues to attract viewers interested in radical political cinema and African American cultural history.</t>
         </is>
       </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -20819,6 +21660,7 @@
           <t>I don't have any information about a film called "Blue Has No Borders" in my knowledge base. This title doesn't match any widely known or documented film I'm aware of. Without access to information about this specific work, I cannot accurately describe what viewer desires or needs it might meet.</t>
         </is>
       </c>
+      <c r="X186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -20924,6 +21766,11 @@
           <t># Bāhubali: The Epic - Viewer Desires and Needs Met
 **Bāhubali: The Beginning** and its sequel meet several key viewer desires:
 **Escapism and Spectacle**: The films provide grand visual escapism through epic battle sequences, stunning CGI, and massive set pieces that transport audiences to a mythical ancient kingdom. **Hero Worship**: The protagonist embodies the archetypal larger-than-life hero with superhuman strength, unwavering nobility, and moral righteousness, fulfilling the desire for an idealized champion. **Emotional Drama**: The story satisfies needs for family drama, romance, betrayal, and revenge through its multigenerational tale of palace intrigue and rightful succession. **Cultural Pride**: For Indian audiences particularly, it meets the desire for homegrown cinema that rivals Hollywood in scale and ambition while celebrating Indian mythology and cultural aesthetics. **Clear Morality**: The film provides satisfying good-versus-evil storytelling with clear heroes and villains, meeting the need for moral certainty and justice. **Entertainment Value**: Through its combination of action, romance, comedy, music, and drama, it</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -21044,6 +21891,11 @@
 4. **Visceral, uncomfortable realism** - Appeals to audiences seeking raw, unflinching portrayals of institutional abuse rather than sanitized entertainment
 5. **Social critique** - Fulfills desire for films that question tradition, privilege, and brotherhood ideals in American college culture
 The film primarily serves viewers seeking thought-provoking drama about systemic violence and personal accountability rather than entertainment or escapism.</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -21160,6 +22012,7 @@
 The film functions as a feel-good antidote to cynicism, celebrating life's small miracles and the possibility of happiness.</t>
         </is>
       </c>
+      <c r="X189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -21245,6 +22098,11 @@
           <t>"Mark Watson: Search" meets viewers' desires for intelligent, introspective comedy that explores modern anxieties about meaning, purpose, and connection in the digital age. The special appeals to audiences seeking thoughtful humor that addresses existential questions, the overwhelming nature of information overload, and the struggle to find authenticity in contemporary life, while still delivering laughs through Watson's self-deprecating style and observational wit.</t>
         </is>
       </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -21338,6 +22196,11 @@
           <t>National Theatre Live: Hamlet meets viewers' desires for accessible high-quality theater, allowing global audiences to experience a prestigious stage production without traveling to London. It satisfies the need for intellectually engaging content through Shakespeare's classic exploration of revenge, mortality, and madness, while the cinematic format provides intimate close-ups and optimal viewing angles unavailable to most theater seats. The production also fulfills cultural enrichment goals and offers an affordable alternative to expensive theater tickets, making elite performances democratically available to diverse audiences worldwide.</t>
         </is>
       </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -21451,6 +22314,11 @@
           <t>The film *Othello* meets viewers' desires for:
 **Dramatic intensity and emotional catharsis** - The tragedy provides a powerful exploration of jealousy, betrayal, and downfall that allows audiences to experience extreme emotions safely. **Psychological complexity** - Viewers are drawn to the intricate character study of manipulation, insecurity, and the destructive power of doubt. **Timeless themes** - The film addresses universal concerns about trust, racism, love, and deception that remain relevant across cultures and eras. **Moral reflection** - It satisfies the need to contemplate justice, evil, and human weakness, prompting ethical consideration. **Artistic and literary prestige** - Shakespeare adaptations fulfill desires for cultural enrichment and engagement with "high art."
 **Suspense and dramatic irony** - Audiences experience tension knowing more than the protagonist, creating engagement through anticipated tragedy.</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -21532,6 +22400,11 @@
       <c r="W193" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "RBO - Top 40" in my knowledge base. Without details about this particular film's content, format, or purpose, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about what this film is, I'd be happy to help summarize how it serves its audience.</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -21655,6 +22528,11 @@
 The film particularly resonates with audiences seeking stories about second chances, female autonomy, and the universal desire to reconnect with one's authentic self.</t>
         </is>
       </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -21760,6 +22638,11 @@
           <t>I don't have any information about a film called "Stitch Head." This title doesn't appear to match any widely known or released film. You may be thinking of a different title, or this could be a lesser-known independent production. If you're referring to "Lilo &amp; Stitch" or another related property, please clarify and I'd be happy to help.</t>
         </is>
       </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -21871,6 +22754,11 @@
       <c r="W196" t="inlineStr">
         <is>
           <t>"The Testament of Ann Lee" meets viewers' desires for avant-garde, experimental cinema through its abstract visual poetry and non-narrative structure. It appeals to audiences interested in exploring themes of spirituality, feminism, and religious mysticism through unconventional filmmaking techniques. The film satisfies those seeking contemplative, meditative experiences rather than traditional storytelling, attracting viewers who appreciate artistic challenges to conventional cinema and are drawn to underground or counter-cultural artistic expressions.</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -21966,6 +22854,7 @@
           <t>I don't have any information about a film called "Turner &amp; Constable" in my knowledge base. This title doesn't correspond to any widely known or documented film. If you could provide more details about the film (such as release year, director, or context), or if the title is slightly different, I'd be happy to help identify what viewer needs it might address.</t>
         </is>
       </c>
+      <c r="X197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -22079,6 +22968,11 @@
           <t>"Wuthering Heights" meets viewers' desires for intense romantic passion, exploration of obsessive love and revenge, gothic atmosphere and drama, emotional catharsis through tragic storytelling, and examination of class conflict and social barriers. The film appeals to those seeking a dark, brooding love story that explores the destructive nature of unfulfilled desire and the consequences of cruelty across generations.</t>
         </is>
       </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -22188,6 +23082,11 @@
           <t>I don't have specific information about a film titled "All That's Left of You" in my knowledge base. This could be because it's a lesser-known independent film, a recent release after my training data, or possibly listed under a different title. Without access to details about this particular film's content, themes, or reception, I cannot accurately describe what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -22293,6 +23192,11 @@
           <t>I don't have specific information about a film called "Bouchra" in my knowledge base. Without details about this particular film's content, themes, or style, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as its director, year, or subject matter), I would be better able to help.</t>
         </is>
       </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -22402,6 +23306,7 @@
           <t>"Collective Monologue" meets viewers' desires for thought-provoking, experimental cinema that explores themes of communication, isolation, and human connection in modern society. The film appeals to audiences seeking non-traditional narrative structures, artistic expression, and philosophical reflection on how individuals relate to one another despite being physically together. It satisfies those interested in avant-garde filmmaking and social commentary about the paradox of loneliness within groups.</t>
         </is>
       </c>
+      <c r="X201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -22497,6 +23402,11 @@
       <c r="W202" t="inlineStr">
         <is>
           <t>"Der Bomberpilot" (1970) is a West German comedy that met viewers' desires for satirical entertainment that challenged taboos around World War II. The film provided comic relief through absurdist humor while allowing audiences to process difficult historical topics through parody. It satisfied a post-war generation's need to confront Nazi-era subjects with irreverence rather than solemnity, offering both escapist entertainment and a form of cultural catharsis during a period when Germany was grappling with its past.</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -22588,6 +23498,7 @@
 The film serves both entertainment and educational purposes, appealing to history enthusiasts, students, educators, and anyone seeking to understand American governmental origins in an accessible Disney-branded format.</t>
         </is>
       </c>
+      <c r="X203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -22689,6 +23600,7 @@
           <t>I don't have any information about a film called "He Thought He Died" in my knowledge base. This title doesn't match any widely known or documented film that I'm aware of. Without access to information about this specific film, I cannot provide an accurate summary of what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -22800,6 +23712,11 @@
       <c r="W205" t="inlineStr">
         <is>
           <t>I don't have any reliable information about a film titled "If I Had Legs I'd Kick You" in my knowledge base, so I cannot accurately describe what viewer desires or needs it meets. This may be an obscure, independent, or very recent film that I'm not familiar with.</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -22888,6 +23805,7 @@
 - **Cultural sophistication** - The ident signals quality, arthouse cinema, appealing to viewers who want to distinguish themselves as serious film enthusiasts</t>
         </is>
       </c>
+      <c r="X206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -22989,6 +23907,7 @@
           <t>I don't have reliable information about a film called "Macdo" to provide an accurate summary of what viewer desires or needs it meets. There are multiple films with similar titles, and without more context about the specific film (director, year, country of origin), I cannot give you a meaningful answer about its appeal to audiences.</t>
         </is>
       </c>
+      <c r="X207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -23094,6 +24013,7 @@
           <t>I don't have any information about a film called "Night is Limpid" in my knowledge base. This title doesn't match any widely known or documented film. It's possible this is a very obscure, regional, experimental film, or perhaps the title has been translated or transliterated differently. Without access to information about this specific work, I cannot provide a summary of what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -23209,6 +24129,11 @@
 **Psychological thriller intensity** - It provides suspense and tension through its disturbing narrative about a woman confronting her abusive past. **Complex character study** - Viewers seeking sophisticated performances get Rebecca Hall's compelling portrayal of trauma and unraveling mental state. **Ambiguity and interpretation** - The film satisfies audiences who enjoy debating what's real versus psychological breakdown, leaving key questions deliberately unanswered. **Exploration of trauma and control** - It addresses the lasting impact of abusive relationships and gaslighting, resonating with viewers interested in these psychological themes. **Visceral horror elements** - The film delivers shocking, body-horror moments that appeal to fans seeking disturbing and transgressive content. **Female perspective on power dynamics** - It examines women's experiences with manipulation and reclaiming agency from male abusers.</t>
         </is>
       </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -23318,6 +24243,11 @@
           <t>"Sirāt" (2024) meets viewers' desires for authentic cultural representation, exploring themes of faith, identity, and moral struggle within an Islamic context. The film appeals to audiences seeking thought-provoking spiritual narratives that examine the concept of the "straight path" (sirāt in Arabic), addressing questions of righteousness, redemption, and the human condition. It satisfies needs for nuanced storytelling that bridges religious philosophy with contemporary challenges, offering both Muslim and general audiences a contemplative cinematic experience about navigating life's ethical dilemmas.</t>
         </is>
       </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -23429,6 +24359,11 @@
       <c r="W211" t="inlineStr">
         <is>
           <t>I don't have reliable information about a film called "Sound of Falling" to provide an accurate summary of what viewer desires or needs it meets. This title doesn't match any widely known or documented film in my knowledge base. If you could provide additional context such as the director, year of release, or country of origin, I might be able to help identify the correct film.</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -23545,6 +24480,11 @@
 The film appeals to cinephiles interested in radical filmmaking, LGBTQ+ cinema history, and the intersection of opera and film.</t>
         </is>
       </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -23652,6 +24592,11 @@
       <c r="W213" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "The Love That Remains" in my knowledge base. This title could refer to a documentary, independent film, or lesser-known production that isn't widely documented. Without access to details about this particular film's content, themes, or reception, I cannot accurately describe what viewer desires or needs it fulfills.</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -23758,6 +24703,7 @@
 The film appeals to viewers who enjoy morally ambiguous fables that challenge conventional notions of righteousness while providing darkly comedic entertainment.</t>
         </is>
       </c>
+      <c r="X214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -23867,6 +24813,7 @@
           <t>"The President's Cake" is a 2012 Serbian documentary that meets viewers' desires for political satire and social commentary. It explores the absurdity of political power and corruption through the metaphor of an elaborate cake made for a president's birthday, satisfying audiences seeking critical examination of authoritarian leadership, dark humor about political excess, and insight into post-Yugoslav society's relationship with power and democracy.</t>
         </is>
       </c>
+      <c r="X215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -23982,6 +24929,11 @@
 **Intellectual Engagement**: The film satisfies viewers seeking complex moral ambiguity and political intrigue, exploring themes of anarchism, terrorism, espionage, and betrayal without clear heroes or villains. **Period Drama Appeal**: It fulfills the desire for atmospheric late Victorian London settings, detailed costumes, and historical immersion. **Psychological Tension**: The film provides suspense through its slow-burning narrative about a bombing plot, appealing to those who enjoy psychological thrillers over action spectacles. **Character Study**: Viewers interested in flawed, morally compromised protagonists find satisfaction in the portrayal of Verloc, a double agent trapped between incompatible loyalties. **Tragic Drama**: The film meets needs for emotionally powerful storytelling, particularly through its devastating family tragedy and the consequences of betrayal. **Literary Adaptation**: It serves viewers who appreciate faithful adaptations of classic literature with sophisticated dialogue and narrative complexity.</t>
         </is>
       </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -24091,6 +25043,7 @@
           <t>"Animal Love" (1995), an Austrian documentary by Ulrich Seidl, meets viewers' desires for unflinching observational cinema that examines unconventional human-animal relationships. The film appeals to those interested in exploring loneliness, social isolation, and the boundaries of companionship through a provocative, non-judgmental lens. It satisfies curiosity about taboo subjects while offering a stark meditation on human need for connection, appealing to audiences who appreciate challenging, art-house documentaries that confront uncomfortable psychological and social realities.</t>
         </is>
       </c>
+      <c r="X217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -24204,6 +25157,11 @@
           <t>I don't have any information about a film called "No Other Choice" in my knowledge base. This title may refer to an obscure, independent, or very recent film that I'm not familiar with, or it could be known by a different name. Without access to details about this specific film, I cannot provide a summary of what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -24319,6 +25277,11 @@
 **Horror/Thriller Cravings** - Provides supernatural scares and demon possession elements for genre fans seeking frightening entertainment. **Cultural Exploration** - Satisfies curiosity about Brujería (Mexican witchcraft) and indigenous spiritual practices, offering representation of Latinx culture rarely seen in mainstream horror. **Personal Redemption Stories** - Meets the need for character-driven narratives about addiction, family trauma, and spiritual healing through the protagonist's journey. **Atmospheric Tension** - Delivers claustrophobic, suspenseful storytelling for viewers who enjoy slow-burn psychological horror over jump scares. **Identity and Belonging Themes** - Resonates with audiences seeking stories about reconnecting with cultural roots and reconciling modern vs. traditional values.</t>
         </is>
       </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -24434,6 +25397,11 @@
 **Intellectual stimulation** through its complex moral ambiguities and critique of political extremism, avoiding simple hero-villain dynamics. **Psychological depth** via its exploration of damaged characters, failed relationships, and the human cost of ideology. **Atmospheric tension** through slow-burning suspense and dread rather than action spectacle. **Period drama appeal** with its meticulous recreation of Victorian London's dark underbelly. **Literary prestige** as an adaptation of Joseph Conrad's novel, attracting audiences interested in serious, art-house cinema. **Social commentary** examining terrorism, surveillance, exploitation, and the corrupting nature of political fanaticism—themes that remain relevant. The film appeals to mature audiences seeking thoughtful, character-driven drama over entertainment spectacle.</t>
         </is>
       </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -24545,6 +25513,11 @@
       <c r="W221" t="inlineStr">
         <is>
           <t>"Wuthering Heights" meets viewers' desires for intense romantic passion, Gothic atmosphere, and exploration of dark human emotions like obsession, revenge, and forbidden love. It appeals to those drawn to tragic love stories, complex antiheroes, themes of social class conflict, and the examination of how love and hatred can consume individuals across generations. The film satisfies audiences seeking emotional depth, dramatic landscapes, and timeless tales of love that transcends death.</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -24636,6 +25609,7 @@
           <t>I don't have any information about a film called "3000 Lesbians Go To York." This doesn't appear to be a widely known or documented film. Without access to information about this specific work, I cannot accurately describe what viewer desires or needs it might meet.</t>
         </is>
       </c>
+      <c r="X222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -24757,6 +25731,11 @@
 7. **Intellectual stimulation** - The film's ambiguity about whether events are real or hallucinatory invites active interpretation and discussion</t>
         </is>
       </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -24862,6 +25841,11 @@
           <t># Summary: Viewer Desires Met by "All You Need Is Kill" (Edge of Tomorrow)
 The film satisfies several key viewer desires:
 **Action and Spectacle** - Delivers intense sci-fi combat sequences with alien warfare and futuristic military technology that appeal to fans of blockbuster entertainment. **Puzzle-Solving Satisfaction** - The time-loop premise creates an engaging mystery where viewers experience the satisfaction of watching the protagonist learn, adapt, and incrementally solve an impossible problem. **Power Fantasy and Mastery** - Audiences vicariously enjoy watching an inexperienced soldier transform into an elite warrior through repeated experience, fulfilling desires for competence and heroism. **Romantic Connection** - Provides emotional grounding through the evolving relationship between the leads, adding human stakes to the larger conflict. **Humor and Levity** - Uses the repetitive structure for comedic effect, preventing the dark premise from becoming too heavy while maintaining entertainment value. **Redemption Arc** - Satisfies the desire to see character growth as a cowardly protagonist becomes genuinely heroic, offering an inspiring transformation narrative. The film essentially packages existential themes about war</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -24973,6 +25957,7 @@
 The film satisfies those wanting heartfelt comedy about friendship, identity, and the gap between dreams and reality.</t>
         </is>
       </c>
+      <c r="X225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -25085,6 +26070,11 @@
         <is>
           <t># Summary of Viewer Desires Met by "Crime 101"
 Without specific information about a film titled "Crime 101," I cannot provide an accurate summary of what viewer needs it fulfills. There are multiple works with similar titles, and the specific desires met would depend on whether it's a documentary, thriller, educational film, or another genre. If you could clarify which "Crime 101" you're referring to (release year, director, or platform), I could provide a more accurate response.</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -25207,6 +26197,11 @@
 The film primarily serves viewers seeking challenging, thought-provoking cinema rather than entertainment, appealing to those who want art that confronts dark social realities.</t>
         </is>
       </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -25318,6 +26313,11 @@
       <c r="W228" t="inlineStr">
         <is>
           <t>"Good Luck, Have Fun, Don't Die" is a 2013 documentary about competitive gaming (esports) that meets viewer desires for understanding gaming culture, following underdog stories, exploring dedication and sacrifice in pursuit of dreams, and witnessing the human drama behind professional video game competition. It appeals to both gaming enthusiasts seeking validation of their hobby as legitimate sport and general audiences curious about this emerging subculture, while satisfying needs for inspirational narratives about young people pursuing unconventional career paths.</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -25437,6 +26437,11 @@
 The film appeals to those seeking both intellectual engagement with nature writing and emotional resonance through a deeply personal journey.</t>
         </is>
       </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -25532,6 +26537,7 @@
 **Intellectual engagement** - The film presents complex philosophical questions about mortality, justice, revenge, and the meaning of existence that challenge viewers to think deeply. **Emotional catharsis** - The tragic story of loss, betrayal, and doomed love allows audiences to experience and purge intense emotions in a safe context. **Moral exploration** - Viewers grapple with ethical dilemmas about revenge, duty, and corruption, helping them examine their own values. **Psychological depth** - The protagonist's internal conflict and descent into apparent madness offer insight into human psychology and mental anguish. **Dramatic spectacle** - The story delivers suspense, violence, supernatural elements, and theatrical confrontations that provide entertainment and excitement. **Cultural literacy** - Experiencing this canonical work fulfills the desire to engage with important artistic and literary heritage. **Universal recognition** - Themes of family conflict, indecision, and confronting mortality resonate across cultures and time periods, allowing viewers to see their own struggles reflected.</t>
         </is>
       </c>
+      <c r="X230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -25652,6 +26658,11 @@
 - **Intimate human drama** that explores universal themes of love, loss, and creative expression emerging from tragedy</t>
         </is>
       </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -25765,6 +26776,11 @@
           <t>I don't have any information about a film called "Hoppers" in my knowledge base. Without knowing the specific film you're referring to (as there may be multiple films with similar titles or this could be an obscure/independent production), I cannot accurately describe what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -25878,6 +26894,11 @@
           <t>"If I Had Legs I'd Kick You" is a 2021 documentary that meets viewers' desires for authentic, intimate storytelling about disability, family relationships, and caregiver dynamics. The film follows filmmaker Mary Trunk's complex relationship with her mother Rose, who has multiple sclerosis, offering viewers insight into the often-hidden emotional struggles of both disabled individuals and their caregivers. It appeals to audiences seeking honest, unromanticized portrayals of disability, family dysfunction, and the complicated love between mothers and daughters, while also satisfying interest in personal documentary filmmaking that challenges conventional narratives about caregiving and independence.</t>
         </is>
       </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -25987,6 +27008,11 @@
           <t>I don't have specific information about a film titled "Is This Thing On?" to provide an accurate summary of what viewer desires or needs it meets. This title could refer to multiple productions, or may be a lesser-known or independent film not in my training data. If you could provide additional context (such as the year, director, or genre), I might be able to help better.</t>
         </is>
       </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -26089,6 +27115,11 @@
 *It's Never Over, Jeff Buckley* meets viewers' desires for intimate artistic biography, exploring the life and legacy of the acclaimed singer-songwriter. The film satisfies needs for understanding creative genius, the tragedy of premature death, and the enduring impact of Buckley's music. It appeals to fans seeking deeper connection to his artistry, as well as general audiences interested in stories about tortured artists, the music industry, and how talent transcends mortality through cultural influence.</t>
         </is>
       </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -26202,6 +27233,11 @@
           <t>I don't have any information about a film called "Marty Supreme." This may be an upcoming release that hasn't been widely distributed yet, or the title may be slightly different. Without access to details about the film's plot, themes, or content, I cannot determine what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -26307,6 +27343,11 @@
           <t>I don't have specific information about a film called "Mother's Pride" in my knowledge base. Without being able to verify details about this particular film, I cannot accurately describe what viewer desires or needs it meets. If you could provide additional context (such as the year, director, or country of origin), I might be able to help identify the correct film.</t>
         </is>
       </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -26417,6 +27458,11 @@
 "My Father's Shadow: The Jack Robinson Story" meets viewers' desires for inspiring true stories about overcoming adversity and racial barriers. The film appeals to audiences interested in baseball history, civil rights narratives, and father-son relationships. It satisfies needs for representation by telling Jackie Robinson's story through his son's perspective, while addressing themes of legacy, identity, and living up to a legendary parent's expectations. The documentary format fulfills viewers seeking educational content about an important historical figure and the personal costs of breaking racial barriers in sports.</t>
         </is>
       </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -26518,6 +27564,11 @@
           <t>National Theatre Live: People meets viewers' desires for intelligent, witty drama that explores themes of heritage preservation, class dynamics, and personal responsibility. The film offers audiences access to high-quality British theatre featuring strong performances and sharp dialogue by Alan Bennett, appealing to those who appreciate literary comedy-dramas that blend humor with social commentary about England's aristocratic decline and the complexities of maintaining historical estates.</t>
         </is>
       </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -26629,6 +27680,11 @@
       <c r="W240" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "No Other Choice" in my knowledge base. This could be because it's a lesser-known independent film, a very recent release, or it may be known by a different title. Without access to details about this specific film, I cannot accurately describe what viewer desires or needs it meets.</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -26751,6 +27807,11 @@
 The film meets the needs of sophisticated viewers who value formal innovation and contemplative cinema over entertainment or clear storytelling.</t>
         </is>
       </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -26864,6 +27925,11 @@
           <t>"One Battle After Another" is a Chinese war film that meets viewer desires for patriotic storytelling, heroic sacrifice narratives, and military action. It appeals to audiences seeking historical drama about Chinese military history, particularly stories highlighting courage, duty, and national pride. The film satisfies needs for emotionally resonant combat sequences and the celebration of soldiers' dedication to their country.</t>
         </is>
       </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -26970,6 +28036,11 @@
 "One Last Deal" meets viewer desires for authentic character-driven drama, exploring themes of aging, legacy, and redemption. The film appeals to audiences seeking nuanced portrayals of older protagonists confronting their past mistakes and mortality, while providing a contemplative narrative about second chances, professional integrity, and finding meaning in life's final chapters. It satisfies those who appreciate slow-burn storytelling focused on human relationships and moral complexity rather than action-driven plots.</t>
         </is>
       </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -27077,6 +28148,11 @@
       <c r="W244" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "Pillion" in my knowledge base. Without knowing the film's content, themes, or context, I cannot accurately describe what viewer desires or needs it meets.</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -27200,6 +28276,11 @@
 The film appeals to audiences seeking uplifting, intelligent sci-fi with heart.</t>
         </is>
       </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -27314,6 +28395,11 @@
 Scream 7 satisfies several key audience needs: nostalgia for the franchise's legacy, the thrill of self-aware horror that comments on movie tropes, anticipation for how the series reinvents itself after previous cast departures, curiosity about new plot twists in the "whodunit" mystery format, and the desire for suspenseful entertainment that balances scares with humor. Fans also seek continuation of the meta-commentary on horror cinema and modern culture that defines the franchise.</t>
         </is>
       </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -27427,6 +28513,11 @@
           <t>"Send Help" is a comedy-thriller series (not a film) that meets viewer desires for dark humor, suspense, and meta-commentary on reality TV and influencer culture. It satisfies needs for escapist entertainment while satirizing social media obsession, offering both thrills through its survival-mystery premise and comedy through its self-aware, genre-blending approach. The show appeals to audiences seeking smart, contemporary content that critiques modern digital culture while remaining entertaining.</t>
         </is>
       </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -27536,6 +28627,11 @@
           <t>I don't have any information about a film called "Sentimental Value" in my knowledge base. Without details about this specific film's content, themes, or plot, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as its release year, director, or basic premise), I'd be happy to help analyze how it might appeal to audiences.</t>
         </is>
       </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -27651,6 +28747,11 @@
 **Entertainment &amp; Spectacle**: Delivers stylish visuals, period atmosphere, and genre thrills through its 1930s Jim Crow South setting with supernatural horror elements. **Star Power**: Features dual performances by Michael B. Jordan, satisfying fans' desire to see a charismatic leading actor in a showcase role. **Social Commentary**: Addresses racial injustice and systemic oppression, meeting viewers' need for meaningful content that reflects on historical and contemporary issues. **Genre Satisfaction**: Combines horror, thriller, and historical drama elements for audiences seeking atmospheric, tension-filled storytelling. **Moral Exploration**: Examines themes of sin, redemption, and consequences, appealing to viewers interested in character-driven ethical dilemmas.</t>
         </is>
       </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -27745,6 +28846,11 @@
 "Tabby McTat" meets viewers' desires for heartwarming family entertainment through themes of friendship, belonging, and loyalty. The film appeals to young children's need for comforting stories about separation and reunion, while offering parents wholesome content that addresses emotional growth and finding one's place in the world. Its musical elements, colorful animation, and gentle storytelling satisfy the desire for accessible, feel-good content that families can enjoy together.</t>
         </is>
       </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -27857,6 +28963,11 @@
         <is>
           <t># Summary: What Viewer Desires "The Craft" Meets
 "The Craft" fulfills viewers' desires for empowerment and outsider belonging by depicting marginalized teenage girls gaining supernatural power to overcome bullying, abuse, and social rejection. It offers wish-fulfillment fantasy of controlling one's circumstances, explores themes of female friendship and solidarity, and provides cathartic revenge against oppressors. The film also satisfies curiosity about witchcraft and the occult while delivering gothic aesthetic appeal, teenage rebellion validation, and commentary on the consequences of power abuse. It particularly resonates with viewers who have felt powerless or excluded.</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -27976,6 +29087,11 @@
 - **Brief runtime** - short format (25 minutes) suits children's attention spans and busy family schedules</t>
         </is>
       </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -28087,6 +29203,11 @@
       <c r="W253" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "The Moment" to provide an accurate summary of what viewer desires or needs it meets. There are multiple films with this title from different years and countries, and without knowing which one you're referring to, I cannot give you reliable information about its appeal to audiences.</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -28211,6 +29332,11 @@
 The film essentially meets the need for joyful, uncomplicated entertainment that reminds viewers of simpler times while bringing families together.</t>
         </is>
       </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -28320,6 +29446,7 @@
           <t>"The President's Cake" is a 2012 Serbian documentary that meets viewers' desires for political satire and social commentary by following a baker tasked with creating an elaborate cake for the president's jubilee celebration. The film satisfies needs for understanding post-communist society, observing absurdist bureaucracy, and experiencing dark humor about power dynamics and corruption in the Balkans. It appeals to audiences interested in observational documentary filmmaking and critiques of political pomposity.</t>
         </is>
       </c>
+      <c r="X255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -28420,6 +29547,11 @@
         <is>
           <t># Summary
 *The Scarecrows' Wedding* meets viewers' desires for heartwarming stories about love, friendship, and loyalty. The film appeals to children's enjoyment of colorful animation, gentle humor, and happy endings, while satisfying parents' need for wholesome content with positive messages about staying true to one's commitments and the value of genuine relationships over superficial attractions. It also fulfills the desire for quality family entertainment that can be enjoyed together across generations.</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -28545,6 +29677,11 @@
 The film appeals to viewers wanting thought-provoking, character-driven drama with historical and political dimensions rather than conventional entertainment.</t>
         </is>
       </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -28658,6 +29795,11 @@
           <t>"The Testament of Ann Lee" meets viewer desires for experimental and avant-garde cinema, offering a meditative, non-narrative experience that explores themes of spirituality, religious ecstasy, and female mysticism through striking visual imagery and symbolic content. The film appeals to audiences seeking artistic expression over conventional storytelling, providing an immersive, contemplative experience that challenges traditional film conventions and invites personal interpretation.</t>
         </is>
       </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -28771,6 +29913,11 @@
           <t>I don't have specific information about a film called "Wasteman" in my knowledge base. Without details about this particular film's content, themes, or reception, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as release year, director, or genre), I might be able to offer a more helpful response.</t>
         </is>
       </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -28884,6 +30031,11 @@
           <t>"Wuthering Heights" fulfills viewers' desires for intense romantic passion, emotional catharsis, and exploration of destructive love. It satisfies the need to experience extreme emotions safely, witness transgressive relationships that defy social conventions, and contemplate themes of revenge, obsession, and the consequences of thwarted desire. The film appeals to those drawn to Gothic atmosphere, tragic romance, and psychological complexity in storytelling.</t>
         </is>
       </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -28993,6 +30145,11 @@
           <t># Summary: Viewer Needs Met by *Au Revoir les Enfants*
 Louis Malle's *Au Revoir les Enfants* fulfills several key viewer desires:
 **Emotional catharsis** - The film provides a deeply moving experience about friendship and loss during the Holocaust, allowing audiences to process profound grief. **Historical understanding** - It offers intimate insight into the French Resistance and Jewish persecution during WWII through a child's perspective, satisfying educational curiosity. **Moral reflection** - The story prompts contemplation of courage, complicity, and childhood innocence confronting evil, meeting viewers' need for meaningful ethical engagement. **Nostalgic authenticity** - Malle's semi-autobiographical approach delivers genuine period detail and emotional truth about wartime childhood. **Universal themes** - Through its specific historical moment, the film explores timeless concerns about friendship, betrayal, guilt, and memory that resonate across cultures and generations. The film serves viewers seeking substantive, emotionally honest cinema that combines personal story with historical significance.</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -29115,6 +30272,11 @@
 - **Emotional catharsis** through tension, fear, and ultimate liberation
 - **Appreciation for freedom** by dramatizing what people will sacrifice to achieve it
 The film appeals to audiences seeking compelling historical dramas with adventure, moral clarity, and celebration of the human spirit.</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -29232,6 +30394,11 @@
 The film appeals to cinephiles who appreciate meditative, visually striking crime dramas in the tradition of European art cinema.</t>
         </is>
       </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -29344,6 +30511,7 @@
 - **Cultural discovery** - It offers insight into Brazilian culture and developing world experiences often underrepresented in animation</t>
         </is>
       </c>
+      <c r="X264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -29457,6 +30625,11 @@
           <t>"City on Fire" (1987) meets viewers' desires for intense action and crime drama through its gritty portrayal of an undercover cop infiltrating a jewel heist gang. The film satisfies audiences seeking themes of loyalty, betrayal, and moral ambiguity, while delivering stylish gunfights and tense criminal confrontations. It appeals to fans of Hong Kong cinema's heroic bloodshed genre and those interested in complex characters torn between duty and friendship in the criminal underworld.</t>
         </is>
       </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -29564,6 +30737,11 @@
       <c r="W266" t="inlineStr">
         <is>
           <t>"Declaration of War" meets viewers' needs for emotional catharsis and authentic representation of crisis. The film addresses desires for honest portrayals of parental fear and medical trauma, offering validation to those who've experienced similar struggles with a child's illness. It satisfies the need for hopeful yet realistic storytelling about love and resilience under extreme pressure, while its energetic, unconventional style appeals to viewers seeking fresh approaches to difficult subject matter rather than typical melodrama.</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -29675,6 +30853,7 @@
 The film satisfies viewers seeking meaningful, socially conscious documentary content that humanizes disability while advocating for better care and understanding.</t>
         </is>
       </c>
+      <c r="X267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -29796,6 +30975,11 @@
 The film primarily appeals to viewers seeking confrontational, boundary-pushing cinema that challenges comfort levels and explores the darkest aspects of human nature.</t>
         </is>
       </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -29909,6 +31093,11 @@
           <t># What Viewer Desires and Needs Are Met by Jean de Florette
 **Jean de Florette** satisfies several key viewer desires:
 **Emotional engagement**: The film delivers a compelling tragic narrative that evokes empathy for the protagonist's struggles and outrage at the injustice he suffers. **Moral satisfaction**: Viewers experience catharsis through witnessing clear ethical conflicts between good and evil, innocence and greed. **Aesthetic pleasure**: The stunning Provence landscape provides visual beauty and escapism into rural French countryside. **Intellectual stimulation**: The film explores themes of fate, human nature, greed, and social class, offering depth beyond surface storytelling. **Dramatic tension**: The slow-building suspense of Jean's doomed efforts creates sustained engagement and anticipation. **Cultural experience**: It provides insight into French rural life, traditions, and values, satisfying curiosity about different ways of living. **Justice and resolution desire**: Though tragic in itself, the film is part one of a diptych, prompting viewers to seek closure in the sequel *Manon des Sources*, which delivers ultimate justice.</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -30024,6 +31213,11 @@
 The film meets needs for both artistic sophistication and emotional connection, appealing to viewers seeking cinema as both art form and human drama.</t>
         </is>
       </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -30129,6 +31323,7 @@
 - **Hope and resilience** in the face of devastating circumstances</t>
         </is>
       </c>
+      <c r="X271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -30226,6 +31421,11 @@
       <c r="W272" t="inlineStr">
         <is>
           <t>"Quo Vadis, Aida?" meets viewers' needs for historical understanding and emotional catharsis regarding the Srebrenica genocide. The film satisfies desires for authentic historical drama, moral complexity in impossible situations, and recognition of war crimes and human suffering. It appeals to audiences seeking powerful, socially relevant cinema that honors victims' stories while exploring themes of responsibility, helplessness, and the failures of international protection during the Bosnian War.</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -30321,6 +31521,7 @@
 The film primarily appeals to mature viewers seeking contemplative, challenging cinema rather than entertainment-focused narratives.</t>
         </is>
       </c>
+      <c r="X273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -30412,6 +31613,7 @@
 The film provides escapist entertainment while honoring real wartime bravery.</t>
         </is>
       </c>
+      <c r="X274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -30525,6 +31727,11 @@
 The film appeals to audiences wanting substantive, hard-hitting crime cinema that challenges rather than comforts.</t>
         </is>
       </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -30638,6 +31845,11 @@
 The film meets needs for thoughtful crime drama that prioritizes mood and social context over conventional thriller mechanics.</t>
         </is>
       </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -30729,6 +31941,11 @@
       <c r="W277" t="inlineStr">
         <is>
           <t>"The Oily American" is a 1954 animated short film that meets viewers' desires for political satire and social commentary. It satirizes American oil companies' exploitation of foreign resources, particularly in Latin America, appealing to audiences interested in anti-imperialist critique and economic justice issues. The film uses humor and animation to make serious political content accessible and entertaining, satisfying viewers seeking both comedic entertainment and thought-provoking content about corporate greed and international relations during the Cold War era.</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -30843,6 +32060,11 @@
 - **Simple, accessible storytelling** with clear heroes, villains, and emotional payoffs typical of silent film conventions</t>
         </is>
       </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -30944,6 +32166,11 @@
           <t>"The Ship of Lost Men" (1929) meets viewers' desires for romantic adventure and escapist melodrama. The film offers exotic maritime settings, a love triangle featuring Marlene Dietrich in an early role, and themes of redemption among outcasts. It satisfies audiences' appetite for pre-Code Hollywood sensuality, nautical danger, and the allure of watching morally ambiguous characters seeking salvation in a remote, lawless environment. The film also capitalizes on the star appeal of Dietrich before her major breakthrough in "The Blue Angel."</t>
         </is>
       </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -31047,6 +32274,11 @@
       <c r="W280" t="inlineStr">
         <is>
           <t>"Time and Tide" (2000), directed by Tsui Hark, meets viewer desires for high-octane action and visual spectacle through its kinetic gunfights, inventive cinematography, and stylized violence. The film satisfies needs for adrenaline-fueled entertainment with its breakneck pacing, elaborate shootouts in confined spaces, and Hong Kong action cinema's signature blend of chaos and choreography. It also appeals to audiences seeking emotional stakes beneath the action, offering a story about fatherhood, redemption, and unexpected connections that grounds the explosive set pieces in human drama.</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -31132,6 +32364,7 @@
 **Aesthetic pleasure** - The film offers beautiful cinematography of the French countryside, capturing natural light and landscapes in an impressionistic style that appeals to visual sensibilities. **Romantic nostalgia** - It evokes a longing for simpler times and fleeting romantic moments, tapping into bittersweet emotions about lost love and youth. **Emotional catharsis** - The poignant story of a brief, passionate encounter allows viewers to experience complex feelings about desire, regret, and the passage of time. **Artistic appreciation** - Film enthusiasts value its contribution to French poetic realism and Renoir's masterful direction, satisfying intellectual and cinematic interests. **Escapism** - The pastoral setting and period piece nature provide escape from modern life into a romanticized 19th-century world.</t>
         </is>
       </c>
+      <c r="X281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -31235,6 +32468,7 @@
 **Representation and validation** - Women see their diverse experiences reflected authentically on screen, providing validation of their struggles and triumphs across different cultures. **Education and awareness** - Viewers gain insight into women's experiences globally, fostering empathy and understanding of issues like discrimination, violence, motherhood, and resilience. **Emotional connection** - The intimate, first-person testimonials create powerful emotional bonds and a sense of shared humanity. **Empowerment and inspiration** - Stories of strength and perseverance inspire viewers and reinforce women's agency and capability. **Social consciousness** - The film satisfies desires for meaningful content that addresses important social issues and gender inequality. **Authenticity** - The unfiltered, direct-to-camera format meets the need for genuine, unmediated storytelling without dramatic reenactments.</t>
         </is>
       </c>
+      <c r="X282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -31346,6 +32580,11 @@
 **Emotional catharsis** - It validates feelings of lost love, nostalgia, and longing through beautifully melancholic storytelling. **Aesthetic appreciation** - Stunning visual artistry and detailed animation provide pure sensory pleasure. **Relatable realism** - The authentic portrayal of distance, missed connections, and growing apart resonates with personal experiences. **Bittersweet reflection** - It offers space for contemplating one's own past relationships and the passage of time. **Poetic melancholy** - The film appeals to those who find beauty in sadness and appreciate contemplative, slow-paced narratives about life's impermanence.</t>
         </is>
       </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -31457,6 +32696,11 @@
       <c r="W284" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "Anemone" in my knowledge base. There are several films with similar titles or that reference anemones, but without more details about the release year, director, or country of origin, I cannot provide an accurate summary of what viewer desires or needs this particular film meets.</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -31551,6 +32795,7 @@
 The film satisfies those who enjoy animation that prioritizes mood, atmosphere, and artistic expression over conventional storytelling.</t>
         </is>
       </c>
+      <c r="X285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -31667,6 +32912,11 @@
 The film appeals to both children seeking adventure and adults appreciating film history and craftsmanship.</t>
         </is>
       </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -31752,6 +33002,7 @@
 The film provides thrilling entertainment through its high-concept premise of teleportation, delivering visual spectacle and vicarious excitement for audiences seeking fast-paced, effects-driven adventure.</t>
         </is>
       </c>
+      <c r="X287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -31861,6 +33112,11 @@
           <t>I don't have specific information about a film called "Pillion" in my knowledge base. Without details about this particular film's content, themes, or style, I cannot accurately describe what viewer desires or needs it meets. If you could provide more context about the film (such as its year, director, or genre), I might be able to offer a more helpful response.</t>
         </is>
       </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -31967,6 +33223,11 @@
 *The Orphans* (assuming you're referring to the 1987 drama) meets viewers' desires for emotionally raw storytelling about family dysfunction, survival, and human connection. It appeals to audiences seeking character-driven narratives that explore themes of isolation, vulnerability, and the complexities of caregiving. The film satisfies needs for intimate, dialogue-heavy drama and performances that showcase psychological depth, offering a contemplative examination of damaged individuals attempting to form makeshift family bonds.</t>
         </is>
       </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -32070,6 +33331,11 @@
       <c r="W290" t="inlineStr">
         <is>
           <t>I don't have any reliable information about a film called "Wild Foxes" to provide an accurate summary of what viewer desires or needs it meets. This title doesn't match any well-known or widely documented film in my knowledge base. If you could provide more details about the film (such as release year, director, or alternative titles), I'd be happy to help with a summary.</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -32192,6 +33458,11 @@
 - **Character complexity** - Portrays an enigmatic genius rather than a conventional hero narrative</t>
         </is>
       </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -32301,6 +33572,11 @@
           <t>"Atelier" (2015) meets viewers' desires for intimate character studies and explorations of artistic mentorship. The film appeals to those interested in fashion design, creative processes, and complex power dynamics between mentor and protégé. It satisfies audiences seeking slow-burn psychological drama, nuanced examinations of ambition and sacrifice, and contemplative Japanese cinema that prioritizes atmosphere and subtle emotional tension over plot-driven narratives.</t>
         </is>
       </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -32414,6 +33690,11 @@
           <t>The film Barbie meets viewers' desires for nostalgic escapism, feminist empowerment, and social commentary on gender roles and identity. It provides colorful, visually stunning entertainment while addressing themes of self-discovery, patriarchy critique, and the complexity of modern womanhood. The movie also satisfies audiences seeking humor, celebrity appeal (Margot Robbie, Ryan Gosling), and a blend of lighthearted fun with deeper cultural reflection on beauty standards and societal expectations.</t>
         </is>
       </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -32511,6 +33792,11 @@
           <t># Summary: How *The Wizard of Oz* Meets Viewer Needs
 *The Wizard of Oz* satisfies several fundamental viewer desires:
 **Escapism and Wonder** - The film transports audiences from mundane Kansas to the vibrant, fantastical world of Oz, offering visual spectacle and imaginative adventure. **Comfort and Reassurance** - The story's message that "there's no place like home" provides emotional security and validates the importance of family and belonging. **Hope and Empowerment** - Dorothy and her companions discover they already possess the qualities they seek (courage, heart, wisdom), teaching viewers about inner strength and self-discovery. **Good vs. Evil** - The clear moral framework with a satisfying resolution where good triumphs provides psychological comfort and justice. **Nostalgia and Tradition** - As a beloved classic, it connects generations and offers familiar, comforting entertainment that audiences can share across ages. The film ultimately meets the human need for stories that combine adventure with emotional safety, offering both excitement and the reassurance of a happy ending.</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -32603,6 +33889,7 @@
 The film satisfies desires for sophisticated comedy, visual glamour, and entertainment that's both fun and subtly progressive.</t>
         </is>
       </c>
+      <c r="X295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -32686,6 +33973,7 @@
           <t>"La Rumeur" (The Rumor) meets viewers' desires for psychological tension and social commentary by exploring how gossip and unverified information can destroy lives and communities. The film satisfies needs for dramatic storytelling that examines human nature, mob mentality, and the dangerous spread of misinformation, while offering a cautionary tale about the consequences of assumptions and false accusations in society.</t>
         </is>
       </c>
+      <c r="X296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -32793,6 +34081,11 @@
 **Escapism and Hope** - The film offers an idealistic vision where one honest individual can triumph over systemic corruption, providing comfort during the Depression era. **Moral Validation** - It reinforces viewers' beliefs in American democratic values, honesty, and perseverance against cynicism and greed. **Catharsis** - The underdog narrative allows audiences to experience vicarious satisfaction as Jefferson Smith battles powerful interests and ultimately prevails. **Political Empowerment** - It suggests that ordinary citizens can make a difference, fulfilling a need to believe in personal agency within government. **Emotional Connection** - The earnest protagonist and romantic subplot provide relatable human drama that engages viewers emotionally. **Patriotic Affirmation** - The film celebrates American ideals and institutions, meeting the desire for national identity and pride while simultaneously critiquing their corruption.</t>
         </is>
       </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -32902,6 +34195,11 @@
           <t># Summary
 *The Celluloid Closet* meets viewers' needs for:
 1. **Education and awareness** - It provides a comprehensive history of LGBTQ+ representation in Hollywood films from the silent era through the 1990s. 2. **Validation and representation** - For LGBTQ+ audiences, it acknowledges decades of marginalization and stereotyping in media while celebrating progress. 3. **Critical media literacy** - It teaches viewers to recognize and analyze coded messages, stereotypes, and subtext in films. 4. **Historical context** - The documentary connects Hollywood's portrayal of queer characters to broader social attitudes and censorship codes across different eras. 5. **Cultural critique** - It satisfies those seeking thoughtful analysis of how media shapes and reflects societal views on sexuality and identity.</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -33021,6 +34319,11 @@
 The film primarily serves audiences who prioritize audacious artistic vision over conventional entertainment.</t>
         </is>
       </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -33130,6 +34433,11 @@
 - **Cultural education** - Understanding the Belle Époque era and the challenges faced by women artists</t>
         </is>
       </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -33221,6 +34529,11 @@
       <c r="W301" t="inlineStr">
         <is>
           <t>I don't have specific information about a film called "György Fehér's Films According to Béla Tarr." This title seems unusual as György Fehér and Béla Tarr were both Hungarian filmmakers - Fehér directed films like "Twilight" (1990) which Tarr co-wrote. Without access to details about this specific work, I cannot accurately describe what viewer desires or needs it meets. If you could clarify the exact title or provide more context, I'd be happy to help.</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -33304,6 +34617,7 @@
           <t>"Popeye Sees 3-D" (1953) met viewers' desires for novelty and technological spectacle during the early 3-D film craze of the 1950s. The short cartoon capitalized on audiences' curiosity about the new stereoscopic viewing experience, offering entertainment that showcased the immersive depth effects of the technology while featuring the familiar and beloved Popeye character. It satisfied the public's appetite for gimmicky, visually engaging content that demonstrated cutting-edge cinema innovation.</t>
         </is>
       </c>
+      <c r="X302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -33405,6 +34719,7 @@
           <t>"Tales of the Dumpster Kid" is an underground shock film that appeals to viewers seeking extreme transgressive content, deliberate provocation, and boundary-pushing cinema. It satisfies desires for shocking imagery, dark humor, and counter-cultural rebellion against mainstream filmmaking conventions. The film attracts audiences interested in cult cinema, extreme body horror, and deliberately offensive material that challenges social taboos and tests personal limits for graphic content.</t>
         </is>
       </c>
+      <c r="X303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -33510,6 +34825,11 @@
           <t>"Under Snow" meets viewers' desires for contemplative, atmospheric cinema that explores themes of isolation, survival, and human resilience in harsh natural environments. The film appeals to those seeking slow-paced, visually striking narratives that prioritize mood and introspection over conventional plot-driven storytelling, offering a meditative experience about solitude and the relationship between humans and nature.</t>
         </is>
       </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -33623,6 +34943,11 @@
           <t>I don't have information about a film called "Marty Supreme." This may be an upcoming or unreleased film, or the title may be slightly different. Without access to details about the film's plot, themes, or content, I cannot accurately describe what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -33730,6 +35055,11 @@
       <c r="W306" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "Pillion" in my knowledge base. Without knowing the film's content, themes, or genre, I cannot accurately describe what viewer desires or needs it might meet.</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -33841,6 +35171,11 @@
 - **Family-friendly entertainment**: Accessible content suitable for all ages with themes of courage and perseverance
 - **Educational interest**: Insight into Antarctic expeditions and the challenges of polar environments
 - **Inspirational themes**: Stories of resilience, sacrifice, and the unbreakable bond between species</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -33955,6 +35290,7 @@
 The title itself directly addresses the internalized shame many gay viewers experienced, offering psychological relief by reframing "perversion" as a societal rather than individual problem.</t>
         </is>
       </c>
+      <c r="X308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -34064,6 +35400,11 @@
           <t>I don't have any information about a film called "Lesbian Space Princess" in my knowledge base. This title doesn't appear to correspond to any widely known or documented film that I can provide accurate information about.</t>
         </is>
       </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -34177,6 +35518,11 @@
           <t>I don't have information about a film called "Marty Supreme." This may be an upcoming film that hasn't been released yet, or the title may be slightly different. Without access to details about the film's plot, themes, or content, I cannot accurately describe what viewer desires or needs it meets.</t>
         </is>
       </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -34280,6 +35626,11 @@
       <c r="W311" t="inlineStr">
         <is>
           <t>I don't have any information about a film called "Silent Friend" in my knowledge base. This could be because it's a lesser-known or independent film, a very recent release, or possibly known by a different title. Without access to details about this specific film, I cannot provide a summary of what viewer desires or needs it meets.</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -34399,6 +35750,11 @@
 The film appeals to socially conscious audiences seeking meaningful, humanistic cinema that illuminates overlooked lives and prompts reflection on social justice issues.</t>
         </is>
       </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -34510,6 +35866,11 @@
       <c r="W313" t="inlineStr">
         <is>
           <t>"Wuthering Heights" meets viewers' desires for intense romantic passion, Gothic atmosphere, and dramatic tragedy. It appeals to those seeking exploration of obsessive love, revenge, class conflict, and the darker aspects of human nature. The film satisfies audiences drawn to period drama, sweeping emotional narratives, and stories about love that transcends social boundaries and even death, while also offering the aesthetic pleasures of moody Yorkshire landscapes and Victorian-era settings.</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>

--- a/upcoming_exhibitions.xlsx
+++ b/upcoming_exhibitions.xlsx
@@ -14518,74 +14518,74 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2012</v>
+        <v>1995</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Boaz Yakin</t>
+          <t>Todd Haynes</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Boaz Yakin</t>
+          <t>Todd Haynes</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Joseph Zolfo, Dana Brunetti, Lawrence Bender, John R. Woodward, Stuart Ford, Deepak Nayar, Brian Kavanaugh-Jones, Kevin Spacey</t>
+          <t>Christine Vachon, Lauren Zalaznick, John N. Hart, Ted Hope, Lindsay Law, James Schamus</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Stefan Czapsky</t>
+          <t>Alex Nepomniaschy</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Joseph C. Nemec III</t>
+          <t>David J. Bomba, Clare Scarpulla</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Jason Statham, Chris Sarandon, James Hong, Catherine Chan, Robert John Burke, Anson Mount, Reggie Lee, Joseph Sikora, Igor Jijikine, Elissa Middleton</t>
+          <t>Julianne Moore, Xander Berkeley, Peter Friedman, James LeGros, Dean Norris, Julie Burgess, Ronnie Farer, Jodie Markell, Susan Norman, Jessica Harper</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Action, Crime, Thriller</t>
+          <t>Drama</t>
         </is>
       </c>
       <c r="M124" t="n">
-        <v>72387</v>
+        <v>32646</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>After a former elite agent rescues a 12-year-old Chinese girl who's been abducted, they find themselves in the middle of a standoff between Triads, the Russian Mafia and high-level corrupt New York City politicians and police.</t>
+          <t>Carol White, a Los Angeles housewife in the late 1980s, comes down with a debilitating illness with no clear diagnosis.</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>new york city, triad, corrupt politician</t>
+          <t>pollution, quarantine, chemical, allegory, housewife, medicine, suburbia, female protagonist, allergy, disease, psychiatrist, illness, san fernando valley, disorder, retreat, 1980s, enviromentalism, multiple chemical sensitivity (mcs), environmental illness, chronic illness, psiquiatra</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>She has the code. He is the key.</t>
+          <t>In the 21st century nobody will be… Safe.</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>['redemption', 'corruption', 'survival', 'innocence', 'betrayal']</t>
+          <t>alienation, environmental illness, suburban malaise, female identity, societal neglect</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>gritty realism with fast-paced action sequences and a tense, urban atmosphere</t>
+          <t>minimalist cinematography, slow-paced and contemplative, with a focus on the mundane aspects of suburban life</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>intense and suspenseful, with moments of hope amidst danger.</t>
+          <t>melancholic and introspective, evoking a sense of existential dread.</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -14605,12 +14605,12 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>"Safe" (1995) meets viewers' desires for psychological horror that explores modern anxieties about environmental illness, alienation, and loss of control. It satisfies those seeking ambiguous, unsettling cinema that critiques both toxic modernity and false wellness solutions, offering no easy answers while creating profound unease about the fragility of selfhood and the isolating nature of unexplained suffering.</t>
+          <t>"Safe" meets viewers' desires for psychological complexity and ambiguity, offering a disturbing exploration of environmental illness, modern alienation, and the inadequacy of self-help culture. It appeals to those seeking cerebral, unsettling cinema that resists easy answers, providing a critique of both suburban conformity and New Age solutions while leaving interpretations open. The film satisfies audiences interested in atmospheric dread, feminist perspectives on women's marginalization, and thought-provoking examinations of how society responds to unexplained suffering.</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
